--- a/database/event/5608/event_5608_evp_summary.xlsx
+++ b/database/event/5608/event_5608_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.2447</v>
+        <v>11.1731</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5761</v>
+        <v>5.5406</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1212</v>
+        <v>4.0075</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2447</v>
+        <v>11.1731</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6974</v>
+        <v>4.6258</v>
       </c>
       <c r="G2" t="n">
         <v>6.5473</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0624</v>
+        <v>4.9502</v>
       </c>
       <c r="I2" t="n">
         <v>5.2055</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7423</v>
+        <v>5.6732</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8475</v>
+        <v>2.8133</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8984</v>
+        <v>1.8163</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7423</v>
+        <v>5.6732</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5872</v>
+        <v>4.5181</v>
       </c>
       <c r="G3" t="n">
         <v>1.1551</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8897</v>
+        <v>4.7813</v>
       </c>
       <c r="I3" t="n">
         <v>5.0278</v>
@@ -594,7 +594,7 @@
         <v>2.7848</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8473</v>
+        <v>1.7935</v>
       </c>
       <c r="E4" t="n">
         <v>5.6159</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9177</v>
+        <v>4.8517</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4386</v>
+        <v>2.4059</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5653</v>
+        <v>1.489</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9177</v>
+        <v>4.8517</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9734</v>
+        <v>2.9074</v>
       </c>
       <c r="G5" t="n">
         <v>1.9443</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9734</v>
+        <v>2.9074</v>
       </c>
       <c r="I5" t="n">
         <v>3.0574</v>
@@ -686,7 +686,7 @@
         <v>2.1315</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3151</v>
+        <v>1.2685</v>
       </c>
       <c r="E6" t="n">
         <v>4.2983</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0448</v>
+        <v>4.0383</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0058</v>
+        <v>2.0025</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2126</v>
+        <v>1.1649</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0448</v>
+        <v>4.0383</v>
       </c>
       <c r="F7" t="n">
-        <v>0.882</v>
+        <v>0.8754</v>
       </c>
       <c r="G7" t="n">
         <v>3.1629</v>
       </c>
       <c r="H7" t="n">
-        <v>0.882</v>
+        <v>0.8754</v>
       </c>
       <c r="I7" t="n">
         <v>0.8902</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5842</v>
+        <v>3.5861</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7774</v>
+        <v>1.7783</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0266</v>
+        <v>0.9848</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5842</v>
+        <v>3.5861</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2538</v>
+        <v>-0.2519</v>
       </c>
       <c r="G8" t="n">
         <v>3.838</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2538</v>
+        <v>-0.2519</v>
       </c>
       <c r="I8" t="n">
         <v>-0.2562</v>
@@ -824,7 +824,7 @@
         <v>1.7037</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9665</v>
+        <v>0.9248</v>
       </c>
       <c r="E9" t="n">
         <v>3.4356</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4025</v>
+        <v>3.3925</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6872</v>
+        <v>1.6823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9532</v>
+        <v>0.9077</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4025</v>
+        <v>3.3925</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3457</v>
+        <v>1.3357</v>
       </c>
       <c r="G10" t="n">
         <v>2.0567</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3457</v>
+        <v>1.3357</v>
       </c>
       <c r="I10" t="n">
         <v>1.3583</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0926</v>
+        <v>3.086</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5336</v>
+        <v>1.5303</v>
       </c>
       <c r="D11" t="n">
-        <v>0.828</v>
+        <v>0.7856</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0926</v>
+        <v>3.086</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8878</v>
+        <v>0.8812</v>
       </c>
       <c r="G11" t="n">
         <v>2.2048</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8878</v>
+        <v>0.8812</v>
       </c>
       <c r="I11" t="n">
         <v>0.8961</v>
@@ -962,7 +962,7 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3657</v>
+        <v>0.3323</v>
       </c>
       <c r="E12" t="n">
         <v>1.9484</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9438</v>
+        <v>1.9308</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9639</v>
+        <v>0.9575</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3639</v>
+        <v>0.3253</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9438</v>
+        <v>1.9308</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7442</v>
+        <v>1.7312</v>
       </c>
       <c r="G13" t="n">
         <v>0.1996</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7442</v>
+        <v>1.7312</v>
       </c>
       <c r="I13" t="n">
         <v>1.7605</v>
@@ -1054,7 +1054,7 @@
         <v>0.862</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2809</v>
+        <v>0.2486</v>
       </c>
       <c r="E14" t="n">
         <v>1.7383</v>
@@ -1100,7 +1100,7 @@
         <v>0.5051</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0381</v>
       </c>
       <c r="E15" t="n">
         <v>1.0186</v>
@@ -1146,7 +1146,7 @@
         <v>0.3461</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1394</v>
+        <v>-0.1658</v>
       </c>
       <c r="E16" t="n">
         <v>0.698</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6674</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3342</v>
+        <v>0.331</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1491</v>
+        <v>-0.178</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8689</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-0.195</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8689</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0.877</v>
@@ -1238,7 +1238,7 @@
         <v>0.2771</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1956</v>
+        <v>-0.2213</v>
       </c>
       <c r="E18" t="n">
         <v>0.5588</v>
@@ -1284,7 +1284,7 @@
         <v>0.1825</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2727</v>
+        <v>-0.2973</v>
       </c>
       <c r="E19" t="n">
         <v>0.368</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3474</v>
+        <v>0.3483</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1723</v>
+        <v>0.1727</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.281</v>
+        <v>-0.3051</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3474</v>
+        <v>0.3483</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2425</v>
+        <v>-0.2416</v>
       </c>
       <c r="G20" t="n">
         <v>0.5899</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2425</v>
+        <v>-0.2416</v>
       </c>
       <c r="I20" t="n">
         <v>-0.2436</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1204</v>
+        <v>0.1195</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0597</v>
+        <v>0.0593</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3727</v>
+        <v>-0.3963</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1204</v>
+        <v>0.1195</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2536</v>
+        <v>0.2527</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1332</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2536</v>
+        <v>0.2527</v>
       </c>
       <c r="I21" t="n">
         <v>0.2548</v>
@@ -1422,7 +1422,7 @@
         <v>-0.0828</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4888</v>
+        <v>-0.5104</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1669</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1855</v>
+        <v>-0.1833</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.092</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4963</v>
+        <v>-0.5169</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1855</v>
+        <v>-0.1833</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5667</v>
+        <v>-0.5645</v>
       </c>
       <c r="G23" t="n">
         <v>0.3812</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5667</v>
+        <v>-0.5645</v>
       </c>
       <c r="I23" t="n">
         <v>-0.5693</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2007</v>
+        <v>-0.2002</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0993</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5024</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2007</v>
+        <v>-0.2002</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0648</v>
+        <v>-0.0643</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1359</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0648</v>
+        <v>-0.0643</v>
       </c>
       <c r="I24" t="n">
         <v>-0.0654</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2112</v>
+        <v>-0.2176</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1047</v>
+        <v>-0.1079</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5067</v>
+        <v>-0.5306</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2112</v>
+        <v>-0.2176</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2898</v>
+        <v>0.2834</v>
       </c>
       <c r="G25" t="n">
         <v>-0.501</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2898</v>
+        <v>0.2834</v>
       </c>
       <c r="I25" t="n">
         <v>0.298</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2406</v>
+        <v>-0.2399</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1193</v>
+        <v>-0.119</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5395</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2406</v>
+        <v>-0.2399</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1744</v>
+        <v>-0.1737</v>
       </c>
       <c r="G26" t="n">
         <v>-0.06619999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1744</v>
+        <v>-0.1737</v>
       </c>
       <c r="I26" t="n">
         <v>-0.1752</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1257</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5238</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2535</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2577</v>
+        <v>-0.257</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1278</v>
+        <v>-0.1274</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5255</v>
+        <v>-0.5463</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2577</v>
+        <v>-0.257</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1807</v>
+        <v>-0.18</v>
       </c>
       <c r="G28" t="n">
         <v>-0.077</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1807</v>
+        <v>-0.18</v>
       </c>
       <c r="I28" t="n">
         <v>-0.1815</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1317</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5497</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2656</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5849</v>
+        <v>-0.5844</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.29</v>
+        <v>-0.2898</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6576</v>
+        <v>-0.6767</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5849</v>
+        <v>-0.5844</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0236</v>
+        <v>-0.0231</v>
       </c>
       <c r="G30" t="n">
         <v>-0.5613</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0236</v>
+        <v>-0.0231</v>
       </c>
       <c r="I30" t="n">
         <v>-0.0243</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6652</v>
+        <v>-0.6722</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3299</v>
+        <v>-0.3333</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6901</v>
+        <v>-0.7117</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6652</v>
+        <v>-0.6722</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9428</v>
+        <v>0.9358</v>
       </c>
       <c r="G31" t="n">
         <v>-1.608</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9428</v>
+        <v>0.9358</v>
       </c>
       <c r="I31" t="n">
         <v>0.9516</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7567</v>
+        <v>-0.7577</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3752</v>
+        <v>-0.3757</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7271</v>
+        <v>-0.7458</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7567</v>
+        <v>-0.7577</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1365</v>
+        <v>0.1355</v>
       </c>
       <c r="G32" t="n">
         <v>-0.8932</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1365</v>
+        <v>0.1355</v>
       </c>
       <c r="I32" t="n">
         <v>0.1378</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3874</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7369</v>
+        <v>-0.7551</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7812</v>
@@ -1974,7 +1974,7 @@
         <v>-0.5817</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8952</v>
+        <v>-0.9112</v>
       </c>
       <c r="E34" t="n">
         <v>-1.173</v>
@@ -2020,7 +2020,7 @@
         <v>-0.6294999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9342</v>
+        <v>-0.9496</v>
       </c>
       <c r="E35" t="n">
         <v>-1.2694</v>
@@ -2066,7 +2066,7 @@
         <v>-0.8395</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1053</v>
+        <v>-1.1184</v>
       </c>
       <c r="E36" t="n">
         <v>-1.6929</v>
@@ -2112,7 +2112,7 @@
         <v>-0.9918</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E37" t="n">
         <v>-2</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.2963</v>
+        <v>-2.2941</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.1387</v>
+        <v>-1.1376</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.349</v>
+        <v>-1.3579</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.2963</v>
+        <v>-2.2941</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2963</v>
+        <v>-0.2941</v>
       </c>
       <c r="G38" t="n">
         <v>-2</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2963</v>
+        <v>-0.2941</v>
       </c>
       <c r="I38" t="n">
         <v>-0.2991</v>
@@ -2204,7 +2204,7 @@
         <v>-1.1503</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3584</v>
+        <v>-1.368</v>
       </c>
       <c r="E39" t="n">
         <v>-2.3196</v>
@@ -2250,7 +2250,7 @@
         <v>-1.3745</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5411</v>
+        <v>-1.5482</v>
       </c>
       <c r="E40" t="n">
         <v>-2.7719</v>
@@ -2296,7 +2296,7 @@
         <v>-1.4128</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5723</v>
+        <v>-1.579</v>
       </c>
       <c r="E41" t="n">
         <v>-2.8491</v>

--- a/database/event/5608/event_5608_evp_summary.xlsx
+++ b/database/event/5608/event_5608_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.1731</v>
+        <v>10.1228</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5406</v>
+        <v>5.0197</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0075</v>
+        <v>3.9319</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1731</v>
+        <v>10.1228</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6258</v>
+        <v>3.8932</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5473</v>
+        <v>6.2297</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9502</v>
+        <v>5.1889</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2055</v>
+        <v>6.6084</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1213</v>
+        <v>6.2297</v>
       </c>
       <c r="K2" t="n">
         <v>158</v>
@@ -529,7 +529,7 @@
         <v>240</v>
       </c>
       <c r="M2" t="n">
-        <v>12.3268</v>
+        <v>12.8381</v>
       </c>
       <c r="N2" t="n">
         <v>398</v>
@@ -538,127 +538,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6732</v>
+        <v>5.1331</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8133</v>
+        <v>2.5454</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8163</v>
+        <v>1.6793</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6732</v>
+        <v>5.1331</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5181</v>
+        <v>1.3235</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1551</v>
+        <v>3.8096</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7813</v>
+        <v>1.3235</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0278</v>
+        <v>1.3235</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1551</v>
+        <v>3.8096</v>
       </c>
       <c r="K3" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="L3" t="n">
-        <v>240</v>
+        <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1829</v>
+        <v>5.1331</v>
       </c>
       <c r="N3" t="n">
-        <v>398</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6159</v>
+        <v>4.865</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7848</v>
+        <v>2.4125</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7935</v>
+        <v>1.5583</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6159</v>
+        <v>4.865</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9382</v>
+        <v>2.7004</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6777</v>
+        <v>2.1646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9382</v>
+        <v>2.7004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9382</v>
+        <v>3.4391</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6777</v>
+        <v>2.1646</v>
       </c>
       <c r="K4" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>240</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6159</v>
+        <v>5.6037</v>
       </c>
       <c r="N4" t="n">
-        <v>211</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8517</v>
+        <v>4.8649</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4059</v>
+        <v>2.4124</v>
       </c>
       <c r="D5" t="n">
-        <v>1.489</v>
+        <v>1.5582</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8517</v>
+        <v>4.8649</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9074</v>
+        <v>3.8262</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9443</v>
+        <v>1.0387</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9074</v>
+        <v>5.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0574</v>
+        <v>6.421</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9443</v>
+        <v>1.0387</v>
       </c>
       <c r="K5" t="n">
         <v>158</v>
@@ -667,7 +667,7 @@
         <v>240</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0017</v>
+        <v>7.4597</v>
       </c>
       <c r="N5" t="n">
         <v>398</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2983</v>
+        <v>3.81</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1315</v>
+        <v>1.8893</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2685</v>
+        <v>1.082</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2983</v>
+        <v>3.81</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2983</v>
+        <v>3.81</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2983</v>
+        <v>3.81</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>230</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2983</v>
+        <v>3.81</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0383</v>
+        <v>3.5237</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0025</v>
+        <v>1.7474</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1649</v>
+        <v>0.9528</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0383</v>
+        <v>3.5237</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8754</v>
+        <v>0.8357</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1629</v>
+        <v>2.688</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8754</v>
+        <v>0.8357</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8902</v>
+        <v>0.9058</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1629</v>
+        <v>2.688</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -759,7 +759,7 @@
         <v>206</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0531</v>
+        <v>3.5938</v>
       </c>
       <c r="N7" t="n">
         <v>271</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5861</v>
+        <v>2.9122</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7783</v>
+        <v>1.4441</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9848</v>
+        <v>0.6767</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5861</v>
+        <v>2.9122</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2519</v>
+        <v>-0.1163</v>
       </c>
       <c r="G8" t="n">
-        <v>3.838</v>
+        <v>3.0285</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2519</v>
+        <v>-0.1163</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2562</v>
+        <v>-0.1261</v>
       </c>
       <c r="J8" t="n">
-        <v>3.838</v>
+        <v>3.0285</v>
       </c>
       <c r="K8" t="n">
         <v>65</v>
@@ -805,7 +805,7 @@
         <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5818</v>
+        <v>2.9024</v>
       </c>
       <c r="N8" t="n">
         <v>271</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4356</v>
+        <v>2.8944</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7037</v>
+        <v>1.4353</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9248</v>
+        <v>0.6687</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4356</v>
+        <v>2.8944</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0204</v>
+        <v>0.8555</v>
       </c>
       <c r="G9" t="n">
-        <v>3.456</v>
+        <v>2.039</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0204</v>
+        <v>0.8555</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0204</v>
+        <v>0.9273</v>
       </c>
       <c r="J9" t="n">
-        <v>3.456</v>
+        <v>2.039</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4356</v>
+        <v>2.9663</v>
       </c>
       <c r="N9" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3925</v>
+        <v>2.8486</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6823</v>
+        <v>1.4126</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9077</v>
+        <v>0.648</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3925</v>
+        <v>2.8486</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3357</v>
+        <v>1.2415</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0567</v>
+        <v>1.6071</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3357</v>
+        <v>1.2415</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3583</v>
+        <v>1.3457</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0567</v>
+        <v>1.6071</v>
       </c>
       <c r="K10" t="n">
         <v>65</v>
@@ -897,7 +897,7 @@
         <v>206</v>
       </c>
       <c r="M10" t="n">
-        <v>3.415</v>
+        <v>2.9528</v>
       </c>
       <c r="N10" t="n">
         <v>271</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.086</v>
+        <v>2.6915</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5303</v>
+        <v>1.3347</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7856</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.086</v>
+        <v>2.6915</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8812</v>
+        <v>2.4671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2048</v>
+        <v>0.2244</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8812</v>
+        <v>2.4671</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8961</v>
+        <v>2.6742</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2048</v>
+        <v>0.2244</v>
       </c>
       <c r="K11" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="L11" t="n">
-        <v>206</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1009</v>
+        <v>2.8986</v>
       </c>
       <c r="N11" t="n">
-        <v>271</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9484</v>
+        <v>2.5766</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.2777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3323</v>
+        <v>0.5252</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9484</v>
+        <v>2.5766</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8862</v>
+        <v>-0.0407</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8346</v>
+        <v>2.6173</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8862</v>
+        <v>-0.0407</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8862</v>
+        <v>-0.0407</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8346</v>
+        <v>2.6173</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="L12" t="n">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9484</v>
+        <v>2.5766</v>
       </c>
       <c r="N12" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9308</v>
+        <v>1.7067</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9575</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3253</v>
+        <v>0.1325</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9308</v>
+        <v>1.7067</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7312</v>
+        <v>0.7308</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1996</v>
+        <v>0.9759</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7312</v>
+        <v>0.7308</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7605</v>
+        <v>0.7308</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1996</v>
+        <v>0.9759</v>
       </c>
       <c r="K13" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L13" t="n">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9601</v>
+        <v>1.7067</v>
       </c>
       <c r="N13" t="n">
-        <v>185</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7383</v>
+        <v>1.5432</v>
       </c>
       <c r="C14" t="n">
-        <v>0.862</v>
+        <v>0.7652</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2486</v>
+        <v>0.0587</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7383</v>
+        <v>1.5432</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6631</v>
+        <v>-0.6007</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0752</v>
+        <v>2.1439</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6631</v>
+        <v>-0.6007</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6631</v>
+        <v>-0.6007</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0752</v>
+        <v>2.1439</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7383</v>
+        <v>1.5432</v>
       </c>
       <c r="N14" t="n">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0186</v>
+        <v>1.0752</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5051</v>
+        <v>0.5332</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0381</v>
+        <v>-0.1526</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0186</v>
+        <v>1.0752</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8109</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8295</v>
+        <v>1.6432</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8109</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8109</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8295</v>
+        <v>1.6432</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -1127,7 +1127,7 @@
         <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0186</v>
+        <v>1.0752</v>
       </c>
       <c r="N15" t="n">
         <v>211</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.698</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3461</v>
+        <v>0.3717</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1658</v>
+        <v>-0.2997</v>
       </c>
       <c r="E16" t="n">
-        <v>0.698</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0652</v>
+        <v>-0.7028</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7632</v>
+        <v>1.4523</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0652</v>
+        <v>-0.7028</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0652</v>
+        <v>-0.7028</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7632</v>
+        <v>1.4523</v>
       </c>
       <c r="K16" t="n">
         <v>114</v>
@@ -1173,7 +1173,7 @@
         <v>97</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6980000000000002</v>
+        <v>0.7494999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6674</v>
+        <v>0.699</v>
       </c>
       <c r="C17" t="n">
-        <v>0.331</v>
+        <v>0.3466</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.178</v>
+        <v>-0.3225</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6674</v>
+        <v>0.699</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8624000000000001</v>
+        <v>-0.4491</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.195</v>
+        <v>1.1481</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8624000000000001</v>
+        <v>-0.4491</v>
       </c>
       <c r="I17" t="n">
-        <v>0.877</v>
+        <v>-0.4491</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.195</v>
+        <v>1.1481</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.6989999999999998</v>
       </c>
       <c r="N17" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5588</v>
+        <v>0.6828</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2771</v>
+        <v>0.3386</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2213</v>
+        <v>-0.3298</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5588</v>
+        <v>0.6828</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7097</v>
+        <v>0.8254</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2685</v>
+        <v>-0.1426</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7097</v>
+        <v>0.8254</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7097</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2685</v>
+        <v>-0.1426</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L18" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5588</v>
+        <v>0.7521</v>
       </c>
       <c r="N18" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.368</v>
+        <v>0.591</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1825</v>
+        <v>0.2931</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2973</v>
+        <v>-0.3712</v>
       </c>
       <c r="E19" t="n">
-        <v>0.368</v>
+        <v>0.591</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.5142</v>
       </c>
       <c r="G19" t="n">
-        <v>0.368</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.5142</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
       <c r="J19" t="n">
-        <v>0.368</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="L19" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M19" t="n">
-        <v>0.368</v>
+        <v>0.7317</v>
       </c>
       <c r="N19" t="n">
-        <v>230</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3483</v>
+        <v>0.5735</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1727</v>
+        <v>0.2844</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3051</v>
+        <v>-0.3791</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3483</v>
+        <v>0.5735</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2416</v>
+        <v>-0.1322</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5899</v>
+        <v>0.7057</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2416</v>
+        <v>-0.1322</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2436</v>
+        <v>-0.1376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5899</v>
+        <v>0.7057</v>
       </c>
       <c r="K20" t="n">
         <v>89</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3462999999999999</v>
+        <v>0.5681</v>
       </c>
       <c r="N20" t="n">
         <v>173</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1195</v>
+        <v>0.4471</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0593</v>
+        <v>0.2217</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3963</v>
+        <v>-0.4362</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1195</v>
+        <v>0.4471</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2527</v>
+        <v>0.4523</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1332</v>
+        <v>-0.0052</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2527</v>
+        <v>0.4523</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2548</v>
+        <v>0.4709</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1332</v>
+        <v>-0.0052</v>
       </c>
       <c r="K21" t="n">
         <v>89</v>
@@ -1403,7 +1403,7 @@
         <v>84</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1216</v>
+        <v>0.4657</v>
       </c>
       <c r="N21" t="n">
         <v>173</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1669</v>
+        <v>0.4404</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0828</v>
+        <v>0.2184</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5104</v>
+        <v>-0.4392</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1669</v>
+        <v>0.4404</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0546</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2215</v>
+        <v>0.4404</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0546</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0546</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2215</v>
+        <v>0.4404</v>
       </c>
       <c r="K22" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>230</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1669</v>
+        <v>0.4404</v>
       </c>
       <c r="N22" t="n">
-        <v>109</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1833</v>
+        <v>0.3762</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.1866</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5169</v>
+        <v>-0.4682</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1833</v>
+        <v>0.3762</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5645</v>
+        <v>-0.1158</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3812</v>
+        <v>0.492</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5645</v>
+        <v>-0.1158</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5693</v>
+        <v>-0.1158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3812</v>
+        <v>0.492</v>
       </c>
       <c r="K23" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1881</v>
+        <v>0.3762</v>
       </c>
       <c r="N23" t="n">
-        <v>173</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2002</v>
+        <v>0.2211</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0993</v>
+        <v>0.1096</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5382</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2002</v>
+        <v>0.2211</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0643</v>
+        <v>0.3501</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1359</v>
+        <v>-0.129</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0643</v>
+        <v>0.3501</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0654</v>
+        <v>0.4459</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1359</v>
+        <v>-0.129</v>
       </c>
       <c r="K24" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="L24" t="n">
-        <v>96</v>
+        <v>240</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2013</v>
+        <v>0.3169</v>
       </c>
       <c r="N24" t="n">
-        <v>185</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2176</v>
+        <v>0.1643</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1079</v>
+        <v>0.0815</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5306</v>
+        <v>-0.5638</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2176</v>
+        <v>0.1643</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2834</v>
+        <v>-0.2015</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.501</v>
+        <v>0.3658</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2834</v>
+        <v>-0.2015</v>
       </c>
       <c r="I25" t="n">
-        <v>0.298</v>
+        <v>-0.2098</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.501</v>
+        <v>0.3658</v>
       </c>
       <c r="K25" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="L25" t="n">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.203</v>
+        <v>0.156</v>
       </c>
       <c r="N25" t="n">
-        <v>398</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2399</v>
+        <v>0.122</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.119</v>
+        <v>0.0605</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5395</v>
+        <v>-0.5829</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2399</v>
+        <v>0.122</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1737</v>
+        <v>0.0552</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.0668</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1737</v>
+        <v>0.0552</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1752</v>
+        <v>0.0575</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.0668</v>
       </c>
       <c r="K26" t="n">
         <v>89</v>
@@ -1633,7 +1633,7 @@
         <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2414</v>
+        <v>0.1243</v>
       </c>
       <c r="N26" t="n">
         <v>173</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2535</v>
+        <v>0.1065</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1257</v>
+        <v>0.0528</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5899</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2535</v>
+        <v>0.1065</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3269</v>
+        <v>0.0726</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3269</v>
+        <v>0.0726</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3269</v>
+        <v>0.0756</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="K27" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="L27" t="n">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2535</v>
+        <v>0.1095</v>
       </c>
       <c r="N27" t="n">
-        <v>257</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.257</v>
+        <v>0.0603</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1274</v>
+        <v>0.0299</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5463</v>
+        <v>-0.6108</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.257</v>
+        <v>0.0603</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.18</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.077</v>
+        <v>-0.0053</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.18</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1815</v>
+        <v>0.0711</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.077</v>
+        <v>-0.0053</v>
       </c>
       <c r="K28" t="n">
         <v>89</v>
       </c>
       <c r="L28" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2585</v>
+        <v>0.0658</v>
       </c>
       <c r="N28" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2656</v>
+        <v>-0.0844</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1317</v>
+        <v>-0.0419</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5497</v>
+        <v>-0.6761</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2656</v>
+        <v>-0.0844</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2341</v>
+        <v>0.2732</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4997</v>
+        <v>-0.3576</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2341</v>
+        <v>0.2732</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2341</v>
+        <v>0.2732</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4997</v>
+        <v>-0.3576</v>
       </c>
       <c r="K29" t="n">
         <v>56</v>
@@ -1771,7 +1771,7 @@
         <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2655999999999999</v>
+        <v>-0.08439999999999998</v>
       </c>
       <c r="N29" t="n">
         <v>109</v>
@@ -1780,81 +1780,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5844</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2898</v>
+        <v>-0.047</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6767</v>
+        <v>-0.6808</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5844</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0231</v>
+        <v>0.0927</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5613</v>
+        <v>-0.1874</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0231</v>
+        <v>0.0927</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0243</v>
+        <v>0.0927</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5613</v>
+        <v>-0.1874</v>
       </c>
       <c r="K30" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="L30" t="n">
-        <v>240</v>
+        <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5856</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>398</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6722</v>
+        <v>-0.2802</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1389</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7117</v>
+        <v>-0.7645</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6722</v>
+        <v>-0.2802</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9358</v>
+        <v>0.2227</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.608</v>
+        <v>-0.5029</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9358</v>
+        <v>0.2227</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9516</v>
+        <v>0.2414</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.608</v>
+        <v>-0.5029</v>
       </c>
       <c r="K31" t="n">
         <v>89</v>
@@ -1863,7 +1863,7 @@
         <v>96</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6564000000000001</v>
+        <v>-0.2615</v>
       </c>
       <c r="N31" t="n">
         <v>185</v>
@@ -1872,35 +1872,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7577</v>
+        <v>-0.384</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3757</v>
+        <v>-0.1904</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7458</v>
+        <v>-0.8114</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7577</v>
+        <v>-0.384</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1355</v>
+        <v>1.0421</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8932</v>
+        <v>-1.4261</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1355</v>
+        <v>1.0421</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1378</v>
+        <v>1.1296</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8932</v>
+        <v>-1.4261</v>
       </c>
       <c r="K32" t="n">
         <v>89</v>
@@ -1909,7 +1909,7 @@
         <v>96</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7554</v>
+        <v>-0.2965</v>
       </c>
       <c r="N32" t="n">
         <v>185</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7812</v>
+        <v>-0.4007</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3874</v>
+        <v>-0.1987</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7551</v>
+        <v>-0.8189</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7812</v>
+        <v>-0.4007</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7812</v>
+        <v>-0.4007</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7812</v>
+        <v>-0.4007</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>230</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7812</v>
+        <v>-0.4007</v>
       </c>
       <c r="N33" t="n">
         <v>230</v>
@@ -1964,35 +1964,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.173</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5817</v>
+        <v>-0.3832</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9112</v>
+        <v>-0.9868</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.173</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8506</v>
+        <v>-0.7241</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3224</v>
+        <v>-0.0486</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8506</v>
+        <v>-0.7241</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8506</v>
+        <v>-0.7241</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3224</v>
+        <v>-0.0486</v>
       </c>
       <c r="K34" t="n">
         <v>56</v>
@@ -2001,7 +2001,7 @@
         <v>53</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.173</v>
+        <v>-0.7726999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>109</v>
@@ -2010,35 +2010,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2694</v>
+        <v>-0.8582</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.4256</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9496</v>
+        <v>-1.0254</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2694</v>
+        <v>-0.8582</v>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2694</v>
+        <v>-0.2639</v>
       </c>
       <c r="H35" t="n">
-        <v>-1</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-1</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2694</v>
+        <v>-0.2639</v>
       </c>
       <c r="K35" t="n">
         <v>56</v>
@@ -2047,7 +2047,7 @@
         <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2694</v>
+        <v>-0.8582000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>109</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6929</v>
+        <v>-1.3295</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.8395</v>
+        <v>-0.6593</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1184</v>
+        <v>-1.2382</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6929</v>
+        <v>-1.3295</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5296</v>
+        <v>-0.3278</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.1633</v>
+        <v>-1.0017</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5296</v>
+        <v>-0.3278</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5296</v>
+        <v>-0.3278</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.1633</v>
+        <v>-1.0017</v>
       </c>
       <c r="K36" t="n">
         <v>53</v>
@@ -2093,7 +2093,7 @@
         <v>204</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6929</v>
+        <v>-1.3295</v>
       </c>
       <c r="N36" t="n">
         <v>257</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2</v>
+        <v>-1.4339</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.9918</v>
+        <v>-0.711</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2407</v>
+        <v>-1.2853</v>
       </c>
       <c r="E37" t="n">
-        <v>-2</v>
+        <v>-1.4339</v>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>-0.6832</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>-0.7507</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>-0.6832</v>
       </c>
       <c r="I37" t="n">
-        <v>-1</v>
+        <v>-0.6832</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.7507</v>
       </c>
       <c r="K37" t="n">
         <v>56</v>
@@ -2139,7 +2139,7 @@
         <v>53</v>
       </c>
       <c r="M37" t="n">
-        <v>-2</v>
+        <v>-1.4339</v>
       </c>
       <c r="N37" t="n">
         <v>109</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.2941</v>
+        <v>-1.5916</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.1376</v>
+        <v>-0.7893</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3579</v>
+        <v>-1.3565</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.2941</v>
+        <v>-1.5916</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2941</v>
+        <v>-0.0862</v>
       </c>
       <c r="G38" t="n">
-        <v>-2</v>
+        <v>-1.5054</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2941</v>
+        <v>-0.0862</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2991</v>
+        <v>-0.0934</v>
       </c>
       <c r="J38" t="n">
-        <v>-2</v>
+        <v>-1.5054</v>
       </c>
       <c r="K38" t="n">
         <v>89</v>
@@ -2185,7 +2185,7 @@
         <v>96</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.2991</v>
+        <v>-1.5988</v>
       </c>
       <c r="N38" t="n">
         <v>185</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.3196</v>
+        <v>-1.6251</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.1503</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.368</v>
+        <v>-1.3717</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.3196</v>
+        <v>-1.6251</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.3196</v>
+        <v>-1.6251</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.3196</v>
+        <v>-1.6251</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>230</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.3196</v>
+        <v>-1.6251</v>
       </c>
       <c r="N39" t="n">
         <v>230</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7719</v>
+        <v>-2.2546</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3745</v>
+        <v>-1.118</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5482</v>
+        <v>-1.6559</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.7719</v>
+        <v>-2.2546</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>-1.5251</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7719</v>
+        <v>-0.7295</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>-1.5251</v>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>-1.5251</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7719</v>
+        <v>-0.7295</v>
       </c>
       <c r="K40" t="n">
         <v>114</v>
@@ -2277,7 +2277,7 @@
         <v>97</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.7719</v>
+        <v>-2.2546</v>
       </c>
       <c r="N40" t="n">
         <v>211</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8491</v>
+        <v>-2.4026</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4128</v>
+        <v>-1.1914</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.579</v>
+        <v>-1.7227</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8491</v>
+        <v>-2.4026</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.8491</v>
+        <v>-2.4026</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.8491</v>
+        <v>-2.4026</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>230</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8491</v>
+        <v>-2.4026</v>
       </c>
       <c r="N41" t="n">
         <v>230</v>
@@ -2429,10 +2429,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7452</v>
+        <v>0.6631</v>
       </c>
       <c r="J2" t="n">
-        <v>20.1204</v>
+        <v>17.9037</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2879</v>
+        <v>0.2597</v>
       </c>
       <c r="J3" t="n">
-        <v>7.7733</v>
+        <v>7.0119</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2296</v>
+        <v>0.2227</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1992</v>
+        <v>6.0129</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2125</v>
+        <v>0.2098</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7375</v>
+        <v>5.6646</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3445</v>
+        <v>-0.2061</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.301500000000001</v>
+        <v>-5.5647</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5542</v>
+        <v>0.5062</v>
       </c>
       <c r="J7" t="n">
-        <v>14.9634</v>
+        <v>13.6674</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0199</v>
+        <v>-0.0151</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5373</v>
+        <v>-0.4077</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3936</v>
+        <v>-0.258</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.6272</v>
+        <v>-6.966</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4675</v>
+        <v>-0.3061</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.6225</v>
+        <v>-8.264699999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8007</v>
+        <v>-0.5476</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.6189</v>
+        <v>-14.7852</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0535</v>
+        <v>0.01</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4445</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0285</v>
+        <v>-0.011</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7695</v>
+        <v>-0.297</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3358</v>
+        <v>-0.2265</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.066599999999999</v>
+        <v>-6.1155</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3692</v>
+        <v>-0.2457</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.968400000000001</v>
+        <v>-6.6339</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6756</v>
+        <v>-0.4534</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.2412</v>
+        <v>-12.2418</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.74</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6503</v>
+        <v>1.425</v>
       </c>
       <c r="J17" t="n">
-        <v>44.5581</v>
+        <v>38.475</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.51</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2158</v>
+        <v>1.1416</v>
       </c>
       <c r="J18" t="n">
-        <v>32.8266</v>
+        <v>30.8232</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1836</v>
+        <v>0.2612</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9572</v>
+        <v>7.0524</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2414</v>
+        <v>-0.158</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5178</v>
+        <v>-4.266</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3452</v>
+        <v>-0.2637</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.320399999999999</v>
+        <v>-7.1199</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1964</v>
+        <v>-0.176</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.3208</v>
+        <v>-3.872</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3866</v>
+        <v>-0.2995</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.5052</v>
+        <v>-6.589</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4386</v>
+        <v>-0.3273</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.6492</v>
+        <v>-7.2006</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.55</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6269</v>
+        <v>-0.427</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.7918</v>
+        <v>-9.394</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.53</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6552</v>
+        <v>-0.4457</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.4144</v>
+        <v>-9.805400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8892</v>
+        <v>1.5928</v>
       </c>
       <c r="J27" t="n">
-        <v>41.5624</v>
+        <v>35.0416</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.48</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0731</v>
+        <v>1.0779</v>
       </c>
       <c r="J28" t="n">
-        <v>23.6082</v>
+        <v>23.7138</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.41</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9003</v>
+        <v>0.9818</v>
       </c>
       <c r="J29" t="n">
-        <v>19.8066</v>
+        <v>21.5996</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.289</v>
+        <v>0.3894</v>
       </c>
       <c r="J30" t="n">
-        <v>6.358</v>
+        <v>8.566800000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.12</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2122</v>
+        <v>0.309</v>
       </c>
       <c r="J31" t="n">
-        <v>4.6684</v>
+        <v>6.798</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1339</v>
+        <v>0.1152</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7492</v>
+        <v>3.2256</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1113</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1164</v>
+        <v>2.4752</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.184</v>
+        <v>-0.1245</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.152</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2425</v>
+        <v>-0.1561</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.79</v>
+        <v>-4.3708</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5002</v>
+        <v>-0.3247</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.0056</v>
+        <v>-9.0916</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0062</v>
+        <v>1.0006</v>
       </c>
       <c r="J37" t="n">
-        <v>28.1736</v>
+        <v>28.0168</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6828</v>
+        <v>0.6968</v>
       </c>
       <c r="J38" t="n">
-        <v>19.1184</v>
+        <v>19.5104</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6301</v>
+        <v>0.6505</v>
       </c>
       <c r="J39" t="n">
-        <v>17.6428</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.24</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6301</v>
+        <v>0.6505</v>
       </c>
       <c r="J40" t="n">
-        <v>17.6428</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3343</v>
+        <v>-0.2549</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.3604</v>
+        <v>-7.1372</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1681</v>
+        <v>-0.1585</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.5301</v>
+        <v>-3.3285</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3544</v>
+        <v>-0.2878</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.4424</v>
+        <v>-6.0438</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.6</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5058</v>
+        <v>-0.3734</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.6218</v>
+        <v>-7.8414</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6767</v>
+        <v>-0.4642</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.2107</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8394</v>
+        <v>-0.5784</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.6274</v>
+        <v>-12.1464</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.73</v>
       </c>
       <c r="I47" t="n">
-        <v>1.544</v>
+        <v>1.3668</v>
       </c>
       <c r="J47" t="n">
-        <v>32.424</v>
+        <v>28.7028</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0932</v>
+        <v>1.0975</v>
       </c>
       <c r="J48" t="n">
-        <v>22.9572</v>
+        <v>23.0475</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.49</v>
       </c>
       <c r="I49" t="n">
-        <v>1.071</v>
+        <v>1.0857</v>
       </c>
       <c r="J49" t="n">
-        <v>22.491</v>
+        <v>22.7997</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.48</v>
       </c>
       <c r="I50" t="n">
-        <v>1.0482</v>
+        <v>1.0739</v>
       </c>
       <c r="J50" t="n">
-        <v>22.0122</v>
+        <v>22.5519</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0936</v>
+        <v>0.1869</v>
       </c>
       <c r="J51" t="n">
-        <v>1.9656</v>
+        <v>3.9249</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0076</v>
+        <v>0.9953</v>
       </c>
       <c r="J52" t="n">
-        <v>26.1976</v>
+        <v>25.8778</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.61</v>
+        <v>0.6123</v>
       </c>
       <c r="J53" t="n">
-        <v>15.86</v>
+        <v>15.9198</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4581</v>
+        <v>0.492</v>
       </c>
       <c r="J54" t="n">
-        <v>11.9106</v>
+        <v>12.792</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3085</v>
+        <v>0.3636</v>
       </c>
       <c r="J55" t="n">
-        <v>8.021000000000001</v>
+        <v>9.4536</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2517</v>
+        <v>-0.1754</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.5442</v>
+        <v>-4.5604</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.22</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4368</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>11.3568</v>
+        <v>13.039</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2545</v>
+        <v>0.2667</v>
       </c>
       <c r="J58" t="n">
-        <v>6.617</v>
+        <v>6.9342</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0674</v>
+        <v>-0.0576</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.7524</v>
+        <v>-1.4976</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.79</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3801</v>
+        <v>-0.2406</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.8826</v>
+        <v>-6.2556</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6595</v>
+        <v>-0.44</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.147</v>
+        <v>-11.44</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.92</v>
       </c>
       <c r="I62" t="n">
-        <v>1.961</v>
+        <v>1.6615</v>
       </c>
       <c r="J62" t="n">
-        <v>52.947</v>
+        <v>44.8605</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9307</v>
+        <v>0.9302</v>
       </c>
       <c r="J63" t="n">
-        <v>25.1289</v>
+        <v>25.1154</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2382</v>
+        <v>0.3034</v>
       </c>
       <c r="J64" t="n">
-        <v>6.4314</v>
+        <v>8.191800000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5813</v>
+        <v>-0.515</v>
       </c>
       <c r="J65" t="n">
-        <v>-15.6951</v>
+        <v>-13.905</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8668</v>
+        <v>-0.8257</v>
       </c>
       <c r="J66" t="n">
-        <v>-23.4036</v>
+        <v>-22.2939</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2263</v>
+        <v>0.2293</v>
       </c>
       <c r="J67" t="n">
-        <v>6.1101</v>
+        <v>6.1911</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1299</v>
+        <v>0.1122</v>
       </c>
       <c r="J68" t="n">
-        <v>3.5073</v>
+        <v>3.0294</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.047</v>
+        <v>0.0169</v>
       </c>
       <c r="J69" t="n">
-        <v>1.269</v>
+        <v>0.4563</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3296</v>
+        <v>-0.2085</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.8992</v>
+        <v>-5.6295</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5814</v>
+        <v>-0.3825</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.6978</v>
+        <v>-10.3275</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7342</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>21.2918</v>
+        <v>21.5586</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6317</v>
+        <v>0.6509</v>
       </c>
       <c r="J73" t="n">
-        <v>18.3193</v>
+        <v>18.8761</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6317</v>
+        <v>0.6509</v>
       </c>
       <c r="J74" t="n">
-        <v>18.3193</v>
+        <v>18.8761</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5738</v>
+        <v>0.6046</v>
       </c>
       <c r="J75" t="n">
-        <v>16.6402</v>
+        <v>17.5334</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2286</v>
+        <v>0.2988</v>
       </c>
       <c r="J76" t="n">
-        <v>6.6294</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.55</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8653999999999999</v>
+        <v>1.0655</v>
       </c>
       <c r="J77" t="n">
-        <v>25.0966</v>
+        <v>30.8995</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.8</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J78" t="n">
-        <v>-10.0891</v>
+        <v>-6.4989</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.0891</v>
+        <v>-6.4989</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3787</v>
+        <v>-0.2439</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.9823</v>
+        <v>-7.0731</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.46</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="J81" t="n">
-        <v>-23.0521</v>
+        <v>-15.7528</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7266</v>
+        <v>0.6948</v>
       </c>
       <c r="J82" t="n">
-        <v>26.1576</v>
+        <v>25.0128</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3164</v>
+        <v>0.3012</v>
       </c>
       <c r="J83" t="n">
-        <v>11.3904</v>
+        <v>10.8432</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2453</v>
+        <v>0.2438</v>
       </c>
       <c r="J84" t="n">
-        <v>8.8308</v>
+        <v>8.7768</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1619</v>
+        <v>0.1839</v>
       </c>
       <c r="J85" t="n">
-        <v>5.8284</v>
+        <v>6.6204</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4848</v>
+        <v>-0.4249</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.4528</v>
+        <v>-15.2964</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.24</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4447</v>
+        <v>0.5162</v>
       </c>
       <c r="J87" t="n">
-        <v>16.0092</v>
+        <v>18.5832</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2827</v>
+        <v>0.3102</v>
       </c>
       <c r="J88" t="n">
-        <v>10.1772</v>
+        <v>11.1672</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0684</v>
       </c>
       <c r="J89" t="n">
-        <v>2.7144</v>
+        <v>2.4624</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3947</v>
+        <v>-0.2474</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.2092</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4507</v>
+        <v>-0.2867</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.2252</v>
+        <v>-10.3212</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4014</v>
+        <v>0.4026</v>
       </c>
       <c r="J92" t="n">
-        <v>10.035</v>
+        <v>10.065</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0434</v>
+        <v>-0.0568</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.085</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2284</v>
+        <v>-0.1703</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.71</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3614</v>
+        <v>-0.2383</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.035</v>
+        <v>-5.9575</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8355</v>
+        <v>-0.5745</v>
       </c>
       <c r="J96" t="n">
-        <v>-20.8875</v>
+        <v>-14.3625</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8602</v>
+        <v>0.6448</v>
       </c>
       <c r="J97" t="n">
-        <v>21.505</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.23</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6158</v>
+        <v>0.5085</v>
       </c>
       <c r="J98" t="n">
-        <v>15.395</v>
+        <v>12.7125</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.22</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.4947</v>
       </c>
       <c r="J99" t="n">
-        <v>14.705</v>
+        <v>12.3675</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4612</v>
+        <v>0.439</v>
       </c>
       <c r="J100" t="n">
-        <v>11.53</v>
+        <v>10.975</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1518</v>
       </c>
       <c r="J101" t="n">
-        <v>2.065</v>
+        <v>3.795</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5726</v>
+        <v>0.5414</v>
       </c>
       <c r="J102" t="n">
-        <v>16.6054</v>
+        <v>15.7006</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.534</v>
+        <v>0.5104</v>
       </c>
       <c r="J103" t="n">
-        <v>15.486</v>
+        <v>14.8016</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3589</v>
+        <v>-0.2242</v>
       </c>
       <c r="J104" t="n">
-        <v>-10.4081</v>
+        <v>-6.5018</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.3316</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.8654</v>
+        <v>-9.616400000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5646</v>
+        <v>-0.3693</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.3734</v>
+        <v>-10.7097</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8438</v>
+        <v>0.6227</v>
       </c>
       <c r="J107" t="n">
-        <v>24.4702</v>
+        <v>18.0583</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4367</v>
+        <v>0.3891</v>
       </c>
       <c r="J108" t="n">
-        <v>12.6643</v>
+        <v>11.2839</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2982</v>
+        <v>0.3207</v>
       </c>
       <c r="J109" t="n">
-        <v>8.6478</v>
+        <v>9.3003</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0241</v>
+        <v>0.0298</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.6989</v>
+        <v>0.8642</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1434</v>
+        <v>-0.0798</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.1586</v>
+        <v>-2.3142</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7057</v>
+        <v>0.5216</v>
       </c>
       <c r="J112" t="n">
-        <v>21.171</v>
+        <v>15.648</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4949</v>
+        <v>0.3918</v>
       </c>
       <c r="J113" t="n">
-        <v>14.847</v>
+        <v>11.754</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2088</v>
+        <v>0.1494</v>
       </c>
       <c r="J114" t="n">
-        <v>6.264</v>
+        <v>4.482</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6018</v>
       </c>
       <c r="J115" t="n">
-        <v>-19.188</v>
+        <v>-18.054</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.2337</v>
+        <v>-1.2404</v>
       </c>
       <c r="J116" t="n">
-        <v>-37.011</v>
+        <v>-37.212</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.04</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2845</v>
+        <v>1.1481</v>
       </c>
       <c r="J117" t="n">
-        <v>38.535</v>
+        <v>34.443</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1221</v>
       </c>
       <c r="J118" t="n">
-        <v>2.16</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0086</v>
+        <v>0.0485</v>
       </c>
       <c r="J119" t="n">
-        <v>0.258</v>
+        <v>1.455</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.434</v>
+        <v>-0.2715</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.02</v>
+        <v>-8.145</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5511</v>
+        <v>-0.3576</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.533</v>
+        <v>-10.728</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5729</v>
+        <v>0.4483</v>
       </c>
       <c r="J122" t="n">
-        <v>23.4889</v>
+        <v>18.3803</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3862</v>
+        <v>0.3365</v>
       </c>
       <c r="J123" t="n">
-        <v>15.8342</v>
+        <v>13.7965</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1395</v>
+        <v>0.1189</v>
       </c>
       <c r="J124" t="n">
-        <v>5.7195</v>
+        <v>4.8749</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3023</v>
+        <v>-0.1813</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.3943</v>
+        <v>-7.4333</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.539</v>
+        <v>-0.3494</v>
       </c>
       <c r="J126" t="n">
-        <v>-22.099</v>
+        <v>-14.3254</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3063</v>
+        <v>0.2497</v>
       </c>
       <c r="J127" t="n">
-        <v>12.5583</v>
+        <v>10.2377</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2076</v>
+        <v>0.1676</v>
       </c>
       <c r="J128" t="n">
-        <v>8.5116</v>
+        <v>6.8716</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1512</v>
+        <v>0.1241</v>
       </c>
       <c r="J129" t="n">
-        <v>6.1992</v>
+        <v>5.0881</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1056</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>4.3296</v>
+        <v>3.8417</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2906</v>
+        <v>-0.1725</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.9146</v>
+        <v>-7.0725</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.21</v>
       </c>
       <c r="I132" t="n">
-        <v>2.0636</v>
+        <v>1.6287</v>
       </c>
       <c r="J132" t="n">
-        <v>41.272</v>
+        <v>32.574</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.86</v>
       </c>
       <c r="I133" t="n">
-        <v>1.7451</v>
+        <v>1.2394</v>
       </c>
       <c r="J133" t="n">
-        <v>34.902</v>
+        <v>24.788</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5784</v>
+        <v>0.5477</v>
       </c>
       <c r="J134" t="n">
-        <v>11.568</v>
+        <v>10.954</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3235</v>
+        <v>0.3908</v>
       </c>
       <c r="J135" t="n">
-        <v>6.47</v>
+        <v>7.816</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7348</v>
+        <v>-0.6781</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.696</v>
+        <v>-13.562</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.82</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1512</v>
+        <v>-0.1461</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.024</v>
+        <v>-2.922</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.7</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3376</v>
+        <v>-0.2771</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.752</v>
+        <v>-5.542</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.59</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.5295</v>
+        <v>-0.3815</v>
       </c>
       <c r="J139" t="n">
-        <v>-10.59</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6613</v>
+        <v>-0.4544</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.226</v>
+        <v>-9.087999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.35</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8772</v>
+        <v>-0.6069</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.544</v>
+        <v>-12.138</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4096</v>
+        <v>0.4101</v>
       </c>
       <c r="J142" t="n">
-        <v>10.6496</v>
+        <v>10.6626</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0677</v>
+        <v>-0.0653</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.7602</v>
+        <v>-1.6978</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.87</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2338</v>
+        <v>-0.1545</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.0788</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4547</v>
+        <v>-0.2939</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.8222</v>
+        <v>-7.6414</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.9038</v>
+        <v>-8.387600000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0191</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>26.4966</v>
+        <v>19.1204</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0191</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>26.4966</v>
+        <v>19.1204</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5172</v>
+        <v>0.4434</v>
       </c>
       <c r="J149" t="n">
-        <v>13.4472</v>
+        <v>11.5284</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.04</v>
       </c>
       <c r="I150" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1312</v>
       </c>
       <c r="J150" t="n">
-        <v>1.8564</v>
+        <v>3.4112</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8112</v>
+        <v>-0.7654</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.0912</v>
+        <v>-19.9004</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.13</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3177</v>
+        <v>0.3372</v>
       </c>
       <c r="J152" t="n">
-        <v>9.2133</v>
+        <v>9.7788</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3018</v>
+        <v>0.3207</v>
       </c>
       <c r="J153" t="n">
-        <v>8.7522</v>
+        <v>9.3003</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2889</v>
+        <v>-0.1856</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.3781</v>
+        <v>-5.3824</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4129</v>
+        <v>-0.2653</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.9741</v>
+        <v>-7.6937</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6153</v>
+        <v>-0.4077</v>
       </c>
       <c r="J156" t="n">
-        <v>-17.8437</v>
+        <v>-11.8233</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8629</v>
+        <v>0.64</v>
       </c>
       <c r="J157" t="n">
-        <v>25.0241</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6479</v>
+        <v>0.5147</v>
       </c>
       <c r="J158" t="n">
-        <v>18.7891</v>
+        <v>14.9263</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5139</v>
+        <v>0.443</v>
       </c>
       <c r="J159" t="n">
-        <v>14.9031</v>
+        <v>12.847</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4132</v>
+        <v>0.3995</v>
       </c>
       <c r="J160" t="n">
-        <v>11.9828</v>
+        <v>11.5855</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4624</v>
+        <v>-0.3922</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.4096</v>
+        <v>-11.3738</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0622</v>
+        <v>0.0274</v>
       </c>
       <c r="J162" t="n">
-        <v>1.866</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0209</v>
+        <v>-0.0373</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.627</v>
+        <v>-1.119</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1607</v>
+        <v>-0.1225</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.821</v>
+        <v>-3.675</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3937</v>
+        <v>-0.2537</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.811</v>
+        <v>-7.611</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4231</v>
+        <v>-0.2732</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.693</v>
+        <v>-8.196</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1039</v>
+        <v>0.7921</v>
       </c>
       <c r="J167" t="n">
-        <v>33.117</v>
+        <v>23.763</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4699</v>
+        <v>0.4399</v>
       </c>
       <c r="J168" t="n">
-        <v>14.097</v>
+        <v>13.197</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4403</v>
+        <v>0.4255</v>
       </c>
       <c r="J169" t="n">
-        <v>13.209</v>
+        <v>12.765</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2692</v>
+        <v>0.3292</v>
       </c>
       <c r="J170" t="n">
-        <v>8.076000000000001</v>
+        <v>9.875999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1191</v>
+        <v>0.1861</v>
       </c>
       <c r="J171" t="n">
-        <v>3.573</v>
+        <v>5.583</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3614</v>
+        <v>0.2993</v>
       </c>
       <c r="J172" t="n">
-        <v>10.4806</v>
+        <v>8.6797</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3011</v>
+        <v>0.2474</v>
       </c>
       <c r="J173" t="n">
-        <v>8.7319</v>
+        <v>7.1746</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2694</v>
+        <v>0.2208</v>
       </c>
       <c r="J174" t="n">
-        <v>7.8126</v>
+        <v>6.4032</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.094</v>
+        <v>-0.042</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.726</v>
+        <v>-1.218</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3394</v>
+        <v>-0.2056</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.842599999999999</v>
+        <v>-5.9624</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4899</v>
+        <v>0.3995</v>
       </c>
       <c r="J177" t="n">
-        <v>14.2071</v>
+        <v>11.5855</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4084</v>
+        <v>0.3522</v>
       </c>
       <c r="J178" t="n">
-        <v>11.8436</v>
+        <v>10.2138</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1501</v>
+        <v>0.1331</v>
       </c>
       <c r="J179" t="n">
-        <v>4.3529</v>
+        <v>3.8599</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0557</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>1.6153</v>
+        <v>1.8879</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.64</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6044</v>
+        <v>-0.3978</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.5276</v>
+        <v>-11.5362</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.74</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2042</v>
+        <v>-0.1847</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.6756</v>
+        <v>-3.3246</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.6</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4179</v>
+        <v>-0.3428</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.5222</v>
+        <v>-6.1704</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.45</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.6882</v>
+        <v>-0.4868</v>
       </c>
       <c r="J184" t="n">
-        <v>-12.3876</v>
+        <v>-8.7624</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.32</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.8842</v>
+        <v>-0.6139</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.9156</v>
+        <v>-11.0502</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9251</v>
+        <v>-0.6442</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.6518</v>
+        <v>-11.5956</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.9248</v>
+        <v>1.4602</v>
       </c>
       <c r="J187" t="n">
-        <v>34.6464</v>
+        <v>26.2836</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.88</v>
       </c>
       <c r="I188" t="n">
-        <v>1.7246</v>
+        <v>1.2328</v>
       </c>
       <c r="J188" t="n">
-        <v>31.0428</v>
+        <v>22.1904</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.6</v>
       </c>
       <c r="I189" t="n">
-        <v>1.1878</v>
+        <v>0.9247</v>
       </c>
       <c r="J189" t="n">
-        <v>21.3804</v>
+        <v>16.6446</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.53</v>
       </c>
       <c r="I190" t="n">
-        <v>1.0441</v>
+        <v>0.8442</v>
       </c>
       <c r="J190" t="n">
-        <v>18.7938</v>
+        <v>15.1956</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.06</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0005</v>
+        <v>0.093</v>
       </c>
       <c r="J191" t="n">
-        <v>0.008999999999999999</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.22</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5021</v>
+        <v>0.5926</v>
       </c>
       <c r="J192" t="n">
-        <v>12.0504</v>
+        <v>14.2224</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0515</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.236</v>
+        <v>-1.6344</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5435</v>
+        <v>-0.3622</v>
       </c>
       <c r="J194" t="n">
-        <v>-13.044</v>
+        <v>-8.6928</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6251</v>
+        <v>-0.4184</v>
       </c>
       <c r="J195" t="n">
-        <v>-15.0024</v>
+        <v>-10.0416</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7771</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.6504</v>
+        <v>-12.7128</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1319</v>
+        <v>1.09</v>
       </c>
       <c r="J197" t="n">
-        <v>27.1656</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0905</v>
+        <v>1.0645</v>
       </c>
       <c r="J198" t="n">
-        <v>26.172</v>
+        <v>25.548</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.26</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6431</v>
+        <v>0.6899</v>
       </c>
       <c r="J199" t="n">
-        <v>15.4344</v>
+        <v>16.5576</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2377</v>
+        <v>0.3165</v>
       </c>
       <c r="J200" t="n">
-        <v>5.7048</v>
+        <v>7.596</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0857</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J201" t="n">
-        <v>-2.0568</v>
+        <v>-0.2016</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7227</v>
+        <v>0.6385</v>
       </c>
       <c r="J202" t="n">
-        <v>21.681</v>
+        <v>19.155</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2412</v>
+        <v>0.2036</v>
       </c>
       <c r="J203" t="n">
-        <v>7.236</v>
+        <v>6.108</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1623</v>
+        <v>0.1493</v>
       </c>
       <c r="J204" t="n">
-        <v>4.869</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2686</v>
+        <v>-0.1554</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.058</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3153</v>
+        <v>-0.1877</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.459</v>
+        <v>-5.631</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6069</v>
+        <v>0.5612</v>
       </c>
       <c r="J207" t="n">
-        <v>18.207</v>
+        <v>16.836</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.97</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0716</v>
+        <v>-0.0478</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.148</v>
+        <v>-1.434</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2684</v>
+        <v>-0.1634</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.052</v>
+        <v>-4.902</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.84</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3162</v>
+        <v>-0.1948</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.486000000000001</v>
+        <v>-5.844</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3616</v>
+        <v>-0.2254</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.848</v>
+        <v>-6.762</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3544</v>
+        <v>0.4017</v>
       </c>
       <c r="J212" t="n">
-        <v>12.404</v>
+        <v>14.0595</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3244</v>
+        <v>0.364</v>
       </c>
       <c r="J213" t="n">
-        <v>11.354</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
       <c r="J214" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3544</v>
+        <v>-0.2188</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.404</v>
+        <v>-7.658</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.82</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3544</v>
+        <v>-0.2188</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.404</v>
+        <v>-7.658</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0755</v>
+        <v>1.0385</v>
       </c>
       <c r="J217" t="n">
-        <v>37.6425</v>
+        <v>36.3475</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0543</v>
+        <v>1.023</v>
       </c>
       <c r="J218" t="n">
-        <v>36.9005</v>
+        <v>35.805</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.09</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2951</v>
+        <v>0.2976</v>
       </c>
       <c r="J219" t="n">
-        <v>10.3285</v>
+        <v>10.416</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6738</v>
+        <v>-0.6199</v>
       </c>
       <c r="J220" t="n">
-        <v>-23.583</v>
+        <v>-21.6965</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8397</v>
+        <v>-0.7986</v>
       </c>
       <c r="J221" t="n">
-        <v>-29.3895</v>
+        <v>-27.951</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.92</v>
       </c>
       <c r="I222" t="n">
-        <v>1.9029</v>
+        <v>1.6042</v>
       </c>
       <c r="J222" t="n">
-        <v>41.8638</v>
+        <v>35.2924</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1995</v>
+        <v>1.1445</v>
       </c>
       <c r="J223" t="n">
-        <v>26.389</v>
+        <v>25.179</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.26</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5693</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J224" t="n">
-        <v>12.5246</v>
+        <v>14.7378</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4264</v>
+        <v>0.526</v>
       </c>
       <c r="J225" t="n">
-        <v>9.380800000000001</v>
+        <v>11.572</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3753</v>
+        <v>-0.2903</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.256600000000001</v>
+        <v>-6.3866</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.88</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.123</v>
+        <v>-0.1194</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.706</v>
+        <v>-2.6268</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2061</v>
+        <v>-0.1748</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.5342</v>
+        <v>-3.8456</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3049</v>
+        <v>-0.2362</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.7078</v>
+        <v>-5.1964</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5448</v>
+        <v>-0.366</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.9856</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.54</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6679</v>
+        <v>-0.4502</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.6938</v>
+        <v>-9.904400000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2749</v>
+        <v>1.1762</v>
       </c>
       <c r="J232" t="n">
-        <v>43.3466</v>
+        <v>39.9908</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7836</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="J233" t="n">
-        <v>26.6424</v>
+        <v>26.8532</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4801</v>
+        <v>0.5344</v>
       </c>
       <c r="J234" t="n">
-        <v>16.3234</v>
+        <v>18.1696</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4521</v>
+        <v>0.5099</v>
       </c>
       <c r="J235" t="n">
-        <v>15.3714</v>
+        <v>17.3366</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5604</v>
+        <v>-0.4918</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.0536</v>
+        <v>-16.7212</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3571</v>
+        <v>0.3926</v>
       </c>
       <c r="J237" t="n">
-        <v>12.1414</v>
+        <v>13.3484</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2607</v>
+        <v>0.2675</v>
       </c>
       <c r="J238" t="n">
-        <v>8.863799999999999</v>
+        <v>9.095000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3604</v>
+        <v>-0.233</v>
       </c>
       <c r="J239" t="n">
-        <v>-12.2536</v>
+        <v>-7.922</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.66</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5457</v>
+        <v>-0.3581</v>
       </c>
       <c r="J240" t="n">
-        <v>-18.5538</v>
+        <v>-12.1754</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5457</v>
+        <v>-0.3581</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.5538</v>
+        <v>-12.1754</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.01</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9065</v>
+        <v>1.4305</v>
       </c>
       <c r="J242" t="n">
-        <v>38.13</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8239</v>
+        <v>1.3278</v>
       </c>
       <c r="J243" t="n">
-        <v>36.478</v>
+        <v>26.556</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.09</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1409</v>
+        <v>0.2319</v>
       </c>
       <c r="J244" t="n">
-        <v>2.818</v>
+        <v>4.638</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3776</v>
+        <v>-0.2924</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.552</v>
+        <v>-5.848</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4081</v>
+        <v>-0.3245</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.162000000000001</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0017</v>
+        <v>-0.0345</v>
       </c>
       <c r="J247" t="n">
-        <v>0.034</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2031</v>
+        <v>-0.177</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.062</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2512</v>
+        <v>-0.2088</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.024</v>
+        <v>-4.176</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.64</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5133</v>
+        <v>-0.3507</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.266</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.27</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.9902</v>
+        <v>-0.6962</v>
       </c>
       <c r="J251" t="n">
-        <v>-19.804</v>
+        <v>-13.924</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.25</v>
       </c>
       <c r="I252" t="n">
-        <v>2.101</v>
+        <v>1.6765</v>
       </c>
       <c r="J252" t="n">
-        <v>46.222</v>
+        <v>36.883</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.7654</v>
       </c>
       <c r="J253" t="n">
-        <v>21.3246</v>
+        <v>16.8388</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.739</v>
+        <v>0.6419</v>
       </c>
       <c r="J254" t="n">
-        <v>16.258</v>
+        <v>14.1218</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6057</v>
+        <v>0.5629</v>
       </c>
       <c r="J255" t="n">
-        <v>13.3254</v>
+        <v>12.3838</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.452</v>
+        <v>-0.37</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.944000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="J257" t="n">
-        <v>2.1362</v>
+        <v>1.3486</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.72</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.3488</v>
+        <v>-0.2739</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.6736</v>
+        <v>-6.0258</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.63</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.5148</v>
+        <v>-0.356</v>
       </c>
       <c r="J259" t="n">
-        <v>-11.3256</v>
+        <v>-7.832</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.62</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5308</v>
+        <v>-0.3651</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.6776</v>
+        <v>-8.0322</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8555</v>
+        <v>-0.5899</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.821</v>
+        <v>-12.9778</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.36</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6217</v>
+        <v>0.4771</v>
       </c>
       <c r="J262" t="n">
-        <v>16.7859</v>
+        <v>12.8817</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1014</v>
+        <v>0.0624</v>
       </c>
       <c r="J263" t="n">
-        <v>2.7378</v>
+        <v>1.6848</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.86</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2701</v>
+        <v>-0.1691</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.2927</v>
+        <v>-4.5657</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J265" t="n">
-        <v>-13.2921</v>
+        <v>-8.5914</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5191</v>
+        <v>-0.3372</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.0157</v>
+        <v>-9.1044</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3493</v>
+        <v>0.2935</v>
       </c>
       <c r="J267" t="n">
-        <v>9.431100000000001</v>
+        <v>7.9245</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3344</v>
+        <v>0.2809</v>
       </c>
       <c r="J268" t="n">
-        <v>9.0288</v>
+        <v>7.5843</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.14</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2555</v>
+        <v>0.2162</v>
       </c>
       <c r="J269" t="n">
-        <v>6.8985</v>
+        <v>5.8374</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.06</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0984</v>
+        <v>0.1048</v>
       </c>
       <c r="J270" t="n">
-        <v>2.6568</v>
+        <v>2.8296</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2538</v>
+        <v>-0.1449</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.8526</v>
+        <v>-3.9123</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1262</v>
+        <v>0.7982</v>
       </c>
       <c r="J272" t="n">
-        <v>30.4074</v>
+        <v>21.5514</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3766</v>
+        <v>0.3466</v>
       </c>
       <c r="J273" t="n">
-        <v>10.1682</v>
+        <v>9.3582</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2059</v>
+        <v>-0.1479</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.5593</v>
+        <v>-3.9933</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2765</v>
+        <v>-0.2161</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.4655</v>
+        <v>-5.8347</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4303</v>
+        <v>-0.3689</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.6181</v>
+        <v>-9.9603</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3367</v>
+        <v>0.3615</v>
       </c>
       <c r="J277" t="n">
-        <v>9.0909</v>
+        <v>9.7605</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1106</v>
+        <v>0.1146</v>
       </c>
       <c r="J278" t="n">
-        <v>2.9862</v>
+        <v>3.0942</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>0.034</v>
+        <v>0.0368</v>
       </c>
       <c r="J279" t="n">
-        <v>0.918</v>
+        <v>0.9936</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0453</v>
+        <v>-0.0211</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.2231</v>
+        <v>-0.5697</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3415</v>
+        <v>-0.2096</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.220499999999999</v>
+        <v>-5.6592</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.4703</v>
+        <v>1.028</v>
       </c>
       <c r="J282" t="n">
-        <v>44.109</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8073</v>
+        <v>0.6035</v>
       </c>
       <c r="J283" t="n">
-        <v>24.219</v>
+        <v>18.105</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6629</v>
+        <v>0.5187</v>
       </c>
       <c r="J284" t="n">
-        <v>19.887</v>
+        <v>15.561</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.783</v>
+        <v>-0.7351</v>
       </c>
       <c r="J285" t="n">
-        <v>-23.49</v>
+        <v>-22.053</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8061</v>
+        <v>-0.7604</v>
       </c>
       <c r="J286" t="n">
-        <v>-24.183</v>
+        <v>-22.812</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.28</v>
       </c>
       <c r="I287" t="n">
-        <v>0.507</v>
+        <v>0.4891</v>
       </c>
       <c r="J287" t="n">
-        <v>15.21</v>
+        <v>14.673</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.171</v>
+        <v>0.1707</v>
       </c>
       <c r="J288" t="n">
-        <v>5.13</v>
+        <v>5.121</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1099</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>3.297</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4454</v>
+        <v>-0.2838</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.362</v>
+        <v>-8.513999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5261</v>
+        <v>-0.3413</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.783</v>
+        <v>-10.239</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2212</v>
+        <v>0.8645</v>
       </c>
       <c r="J292" t="n">
-        <v>32.9724</v>
+        <v>23.3415</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1807</v>
+        <v>0.8385</v>
       </c>
       <c r="J293" t="n">
-        <v>31.8789</v>
+        <v>22.6395</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="J294" t="n">
-        <v>1.7982</v>
+        <v>3.4749</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2472</v>
+        <v>-0.1723</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.6744</v>
+        <v>-4.6521</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.5606</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.8075</v>
+        <v>-15.1362</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.17</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3834</v>
+        <v>0.3893</v>
       </c>
       <c r="J297" t="n">
-        <v>10.3518</v>
+        <v>10.5111</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.96</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0433</v>
+        <v>-0.0512</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.1691</v>
+        <v>-1.3824</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.88</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2054</v>
+        <v>-0.1437</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.5458</v>
+        <v>-3.8799</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.76</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4092</v>
+        <v>-0.2637</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.0484</v>
+        <v>-7.1199</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.63</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5873</v>
+        <v>-0.3876</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.8571</v>
+        <v>-10.4652</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2158</v>
+        <v>0.868</v>
       </c>
       <c r="J302" t="n">
-        <v>31.6108</v>
+        <v>22.568</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7829</v>
+        <v>0.6102</v>
       </c>
       <c r="J303" t="n">
-        <v>20.3554</v>
+        <v>15.8652</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.27</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6813</v>
+        <v>0.5572</v>
       </c>
       <c r="J304" t="n">
-        <v>17.7138</v>
+        <v>14.4872</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.22</v>
       </c>
       <c r="I305" t="n">
-        <v>0.533</v>
+        <v>0.4902</v>
       </c>
       <c r="J305" t="n">
-        <v>13.858</v>
+        <v>12.7452</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3127</v>
+        <v>-0.2303</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.1302</v>
+        <v>-5.9878</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.95</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0161</v>
+        <v>-0.0437</v>
       </c>
       <c r="J307" t="n">
-        <v>-0.4186</v>
+        <v>-1.1362</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.91</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0905</v>
+        <v>-0.0939</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.353</v>
+        <v>-2.4414</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2791</v>
+        <v>-0.2127</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.2566</v>
+        <v>-5.5302</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5455</v>
+        <v>-0.3631</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.183</v>
+        <v>-9.4406</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6528</v>
+        <v>-0.4379</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.9728</v>
+        <v>-11.3854</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.4</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6412</v>
+        <v>0.5978</v>
       </c>
       <c r="J312" t="n">
-        <v>17.3124</v>
+        <v>16.1406</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2723</v>
+        <v>0.3025</v>
       </c>
       <c r="J313" t="n">
-        <v>7.3521</v>
+        <v>8.1675</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.01</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0263</v>
+        <v>0.0363</v>
       </c>
       <c r="J314" t="n">
-        <v>0.7101</v>
+        <v>0.9801</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.84</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3279</v>
+        <v>-0.2</v>
       </c>
       <c r="J315" t="n">
-        <v>-8.853300000000001</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5357</v>
+        <v>-0.3472</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.4639</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.47</v>
       </c>
       <c r="I317" t="n">
-        <v>1.1982</v>
+        <v>0.8478</v>
       </c>
       <c r="J317" t="n">
-        <v>32.3514</v>
+        <v>22.8906</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8327</v>
+        <v>0.6182</v>
       </c>
       <c r="J318" t="n">
-        <v>22.4829</v>
+        <v>16.6914</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1182</v>
+        <v>0.17</v>
       </c>
       <c r="J319" t="n">
-        <v>3.1914</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1182</v>
+        <v>0.17</v>
       </c>
       <c r="J320" t="n">
-        <v>3.1914</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7819</v>
+        <v>-0.7341</v>
       </c>
       <c r="J321" t="n">
-        <v>-21.1113</v>
+        <v>-19.8207</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.43</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5854</v>
+        <v>0.4483</v>
       </c>
       <c r="J322" t="n">
-        <v>13.4642</v>
+        <v>10.3109</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.39</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.4229</v>
       </c>
       <c r="J323" t="n">
-        <v>12.3004</v>
+        <v>9.726699999999999</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.31</v>
       </c>
       <c r="I324" t="n">
-        <v>0.4159</v>
+        <v>0.3721</v>
       </c>
       <c r="J324" t="n">
-        <v>9.5657</v>
+        <v>8.558299999999999</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.26</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3424</v>
+        <v>0.337</v>
       </c>
       <c r="J325" t="n">
-        <v>7.8752</v>
+        <v>7.751</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2575</v>
+        <v>0.2704</v>
       </c>
       <c r="J326" t="n">
-        <v>5.9225</v>
+        <v>6.2192</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.98</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0728</v>
+        <v>0.0218</v>
       </c>
       <c r="J327" t="n">
-        <v>1.6744</v>
+        <v>0.5014</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.082</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J328" t="n">
-        <v>-1.886</v>
+        <v>-2.1229</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.61</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.5681</v>
+        <v>-0.3825</v>
       </c>
       <c r="J329" t="n">
-        <v>-13.0663</v>
+        <v>-8.797499999999999</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.6</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.3918</v>
       </c>
       <c r="J330" t="n">
-        <v>-13.3906</v>
+        <v>-9.0114</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.729</v>
+        <v>-0.4946</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.767</v>
+        <v>-11.3758</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.91</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0432</v>
+        <v>-0.0667</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.9936</v>
+        <v>-1.5341</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.71</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.369</v>
+        <v>-0.2847</v>
       </c>
       <c r="J333" t="n">
-        <v>-8.487</v>
+        <v>-6.5481</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3859</v>
+        <v>-0.2941</v>
       </c>
       <c r="J334" t="n">
-        <v>-8.8757</v>
+        <v>-6.7643</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.534</v>
+        <v>-0.3661</v>
       </c>
       <c r="J335" t="n">
-        <v>-12.282</v>
+        <v>-8.420299999999999</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8071</v>
+        <v>-0.5532</v>
       </c>
       <c r="J336" t="n">
-        <v>-18.5633</v>
+        <v>-12.7236</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.75</v>
       </c>
       <c r="I337" t="n">
-        <v>1.6173</v>
+        <v>1.1341</v>
       </c>
       <c r="J337" t="n">
-        <v>37.1979</v>
+        <v>26.0843</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.49</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1197</v>
+        <v>0.8226</v>
       </c>
       <c r="J338" t="n">
-        <v>25.7531</v>
+        <v>18.9198</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.46</v>
       </c>
       <c r="I339" t="n">
-        <v>1.0564</v>
+        <v>0.7859</v>
       </c>
       <c r="J339" t="n">
-        <v>24.2972</v>
+        <v>18.0757</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I340" t="n">
-        <v>0.379</v>
+        <v>0.4183</v>
       </c>
       <c r="J340" t="n">
-        <v>8.717000000000001</v>
+        <v>9.620900000000001</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.96</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3425</v>
+        <v>-0.2562</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.8775</v>
+        <v>-5.8926</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5608/event_5608_evp_summary.xlsx
+++ b/database/event/5608/event_5608_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.1228</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.0197</v>
+        <v>4.939</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9319</v>
+        <v>3.9098</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1228</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8932</v>
+        <v>3.7692</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2297</v>
+        <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1889</v>
+        <v>5.5247</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6084</v>
+        <v>6.4358</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2297</v>
+        <v>6.7318</v>
       </c>
       <c r="K2" t="n">
         <v>158</v>
@@ -529,7 +529,7 @@
         <v>240</v>
       </c>
       <c r="M2" t="n">
-        <v>12.8381</v>
+        <v>13.1676</v>
       </c>
       <c r="N2" t="n">
         <v>398</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1331</v>
+        <v>5.5375</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5454</v>
+        <v>2.746</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6793</v>
+        <v>1.8966</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1331</v>
+        <v>5.5375</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3235</v>
+        <v>1.2451</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8096</v>
+        <v>4.2924</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3235</v>
+        <v>1.2451</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3235</v>
+        <v>1.2451</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8096</v>
+        <v>4.2924</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1331</v>
+        <v>5.5375</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.865</v>
+        <v>4.9602</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4125</v>
+        <v>2.4597</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5583</v>
+        <v>1.6338</v>
       </c>
       <c r="E4" t="n">
-        <v>4.865</v>
+        <v>4.9602</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7004</v>
+        <v>3.684</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1646</v>
+        <v>1.2762</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7004</v>
+        <v>5.3383</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4391</v>
+        <v>6.2187</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1646</v>
+        <v>1.2762</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>240</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6037</v>
+        <v>7.4949</v>
       </c>
       <c r="N4" t="n">
         <v>398</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8649</v>
+        <v>4.8984</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4124</v>
+        <v>2.429</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5582</v>
+        <v>1.6056</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8649</v>
+        <v>4.8984</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8262</v>
+        <v>2.5696</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0387</v>
+        <v>2.3288</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0417</v>
+        <v>2.8992</v>
       </c>
       <c r="I5" t="n">
-        <v>6.421</v>
+        <v>3.3773</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0387</v>
+        <v>2.3288</v>
       </c>
       <c r="K5" t="n">
         <v>158</v>
@@ -667,7 +667,7 @@
         <v>240</v>
       </c>
       <c r="M5" t="n">
-        <v>7.4597</v>
+        <v>5.7061</v>
       </c>
       <c r="N5" t="n">
         <v>398</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.81</v>
+        <v>4.1915</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8893</v>
+        <v>2.0785</v>
       </c>
       <c r="D6" t="n">
-        <v>1.082</v>
+        <v>1.2839</v>
       </c>
       <c r="E6" t="n">
-        <v>3.81</v>
+        <v>4.1915</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.81</v>
+        <v>4.1915</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.81</v>
+        <v>4.1915</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>230</v>
       </c>
       <c r="M6" t="n">
-        <v>3.81</v>
+        <v>4.1915</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5237</v>
+        <v>3.8516</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7474</v>
+        <v>1.91</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9528</v>
+        <v>1.1291</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5237</v>
+        <v>3.8516</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8357</v>
+        <v>0.8442</v>
       </c>
       <c r="G7" t="n">
-        <v>2.688</v>
+        <v>3.0073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8357</v>
+        <v>0.8442</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9058</v>
+        <v>0.8883</v>
       </c>
       <c r="J7" t="n">
-        <v>2.688</v>
+        <v>3.0073</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -759,7 +759,7 @@
         <v>206</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5938</v>
+        <v>3.8956</v>
       </c>
       <c r="N7" t="n">
         <v>271</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9122</v>
+        <v>3.2297</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4441</v>
+        <v>1.6016</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6767</v>
+        <v>0.846</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9122</v>
+        <v>3.2297</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1163</v>
+        <v>-0.0948</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0285</v>
+        <v>3.3245</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1163</v>
+        <v>-0.0948</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1261</v>
+        <v>-0.0997</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0285</v>
+        <v>3.3245</v>
       </c>
       <c r="K8" t="n">
         <v>65</v>
@@ -805,7 +805,7 @@
         <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9024</v>
+        <v>3.2248</v>
       </c>
       <c r="N8" t="n">
         <v>271</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8944</v>
+        <v>3.1015</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4353</v>
+        <v>1.538</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6687</v>
+        <v>0.7877</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8944</v>
+        <v>3.1015</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8555</v>
+        <v>1.2214</v>
       </c>
       <c r="G9" t="n">
-        <v>2.039</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8555</v>
+        <v>1.2214</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9273</v>
+        <v>1.2852</v>
       </c>
       <c r="J9" t="n">
-        <v>2.039</v>
+        <v>1.88</v>
       </c>
       <c r="K9" t="n">
         <v>65</v>
@@ -851,7 +851,7 @@
         <v>206</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9663</v>
+        <v>3.1652</v>
       </c>
       <c r="N9" t="n">
         <v>271</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8486</v>
+        <v>3.0463</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4126</v>
+        <v>1.5106</v>
       </c>
       <c r="D10" t="n">
-        <v>0.648</v>
+        <v>0.7625</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8486</v>
+        <v>3.0463</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2415</v>
+        <v>0.8561</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6071</v>
+        <v>2.1902</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2415</v>
+        <v>0.8561</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3457</v>
+        <v>0.9008</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6071</v>
+        <v>2.1902</v>
       </c>
       <c r="K10" t="n">
         <v>65</v>
@@ -897,7 +897,7 @@
         <v>206</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9528</v>
+        <v>3.091</v>
       </c>
       <c r="N10" t="n">
         <v>271</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6915</v>
+        <v>2.8229</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3347</v>
+        <v>1.3998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6915</v>
+        <v>2.8229</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4671</v>
+        <v>-0.0562</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2244</v>
+        <v>2.8791</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4671</v>
+        <v>-0.0562</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6742</v>
+        <v>-0.0562</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2244</v>
+        <v>2.8791</v>
       </c>
       <c r="K11" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8986</v>
+        <v>2.8229</v>
       </c>
       <c r="N11" t="n">
-        <v>185</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5766</v>
+        <v>2.5535</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2777</v>
+        <v>1.2662</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5252</v>
+        <v>0.5382</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5766</v>
+        <v>2.5535</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0407</v>
+        <v>2.3568</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6173</v>
+        <v>0.1967</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0407</v>
+        <v>2.4335</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0407</v>
+        <v>2.5605</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6173</v>
+        <v>0.1967</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="L12" t="n">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5766</v>
+        <v>2.7572</v>
       </c>
       <c r="N12" t="n">
-        <v>257</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7067</v>
+        <v>1.7837</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8845</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1325</v>
+        <v>0.1878</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7067</v>
+        <v>1.7837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7308</v>
+        <v>0.717</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9759</v>
+        <v>1.0667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7308</v>
+        <v>0.717</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7308</v>
+        <v>0.717</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9759</v>
+        <v>1.0667</v>
       </c>
       <c r="K13" t="n">
         <v>53</v>
@@ -1035,7 +1035,7 @@
         <v>204</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7067</v>
+        <v>1.7837</v>
       </c>
       <c r="N13" t="n">
         <v>257</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5432</v>
+        <v>1.7613</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7652</v>
+        <v>0.8734</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0587</v>
+        <v>0.1776</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5432</v>
+        <v>1.7613</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6007</v>
+        <v>-0.6583</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1439</v>
+        <v>2.4196</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6007</v>
+        <v>-0.6583</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6007</v>
+        <v>-0.6583</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1439</v>
+        <v>2.4196</v>
       </c>
       <c r="K14" t="n">
         <v>114</v>
@@ -1081,7 +1081,7 @@
         <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5432</v>
+        <v>1.7613</v>
       </c>
       <c r="N14" t="n">
         <v>211</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0752</v>
+        <v>1.2074</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5332</v>
+        <v>0.5987</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1526</v>
+        <v>-0.0746</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0752</v>
+        <v>1.2074</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.6172</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6432</v>
+        <v>1.8246</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.6172</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.6172</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6432</v>
+        <v>1.8246</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -1127,7 +1127,7 @@
         <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0752</v>
+        <v>1.2074</v>
       </c>
       <c r="N15" t="n">
         <v>211</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.9235</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3717</v>
+        <v>0.4579</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2997</v>
+        <v>-0.2038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.9235</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7028</v>
+        <v>-0.7464</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4523</v>
+        <v>1.6699</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7028</v>
+        <v>-0.7464</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7028</v>
+        <v>-0.7464</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4523</v>
+        <v>1.6699</v>
       </c>
       <c r="K16" t="n">
         <v>114</v>
@@ -1173,7 +1173,7 @@
         <v>97</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7494999999999999</v>
+        <v>0.9235</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.699</v>
+        <v>0.8264</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3466</v>
+        <v>0.4098</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3225</v>
+        <v>-0.248</v>
       </c>
       <c r="E17" t="n">
-        <v>0.699</v>
+        <v>0.8264</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4491</v>
+        <v>0.8324</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1481</v>
+        <v>-0.006</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4491</v>
+        <v>0.8324</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4491</v>
+        <v>0.8759</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1481</v>
+        <v>-0.006</v>
       </c>
       <c r="K17" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L17" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6989999999999998</v>
+        <v>0.8699</v>
       </c>
       <c r="N17" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6828</v>
+        <v>0.8076</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3386</v>
+        <v>0.4005</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3298</v>
+        <v>-0.2566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6828</v>
+        <v>0.8076</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8254</v>
+        <v>-0.4801</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1426</v>
+        <v>1.2877</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8254</v>
+        <v>-0.4801</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8947000000000001</v>
+        <v>-0.4801</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1426</v>
+        <v>1.2877</v>
       </c>
       <c r="K18" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7521</v>
+        <v>0.8076000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.591</v>
+        <v>0.7188</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2931</v>
+        <v>0.3564</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3712</v>
+        <v>-0.297</v>
       </c>
       <c r="E19" t="n">
-        <v>0.591</v>
+        <v>0.7188</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5142</v>
+        <v>0.6054</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1134</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5142</v>
+        <v>0.6054</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6549</v>
+        <v>0.7052</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1134</v>
       </c>
       <c r="K19" t="n">
         <v>158</v>
@@ -1311,7 +1311,7 @@
         <v>240</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7317</v>
+        <v>0.8186</v>
       </c>
       <c r="N19" t="n">
         <v>398</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5735</v>
+        <v>0.6143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2844</v>
+        <v>0.3046</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3791</v>
+        <v>-0.3446</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5735</v>
+        <v>0.6143</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1322</v>
+        <v>-0.1511</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7057</v>
+        <v>0.7654</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1322</v>
+        <v>-0.1511</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1376</v>
+        <v>-0.155</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7057</v>
+        <v>0.7654</v>
       </c>
       <c r="K20" t="n">
         <v>89</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5681</v>
+        <v>0.6103999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>173</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4471</v>
+        <v>0.4774</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2217</v>
+        <v>0.2367</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4362</v>
+        <v>-0.4069</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4471</v>
+        <v>0.4774</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4523</v>
+        <v>-0.1268</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0052</v>
+        <v>0.6042</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4523</v>
+        <v>-0.1268</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4709</v>
+        <v>-0.1268</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0052</v>
+        <v>0.6042</v>
       </c>
       <c r="K21" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L21" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4657</v>
+        <v>0.4773999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>173</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4404</v>
+        <v>0.4593</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2184</v>
+        <v>0.2278</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4392</v>
+        <v>-0.4151</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4404</v>
+        <v>0.4593</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4404</v>
+        <v>0.4593</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4404</v>
+        <v>0.4593</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>230</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4404</v>
+        <v>0.4593</v>
       </c>
       <c r="N22" t="n">
         <v>230</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3762</v>
+        <v>0.4455</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1866</v>
+        <v>0.2209</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4682</v>
+        <v>-0.4214</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3762</v>
+        <v>0.4455</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1158</v>
+        <v>0.4286</v>
       </c>
       <c r="G23" t="n">
-        <v>0.492</v>
+        <v>0.0169</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1158</v>
+        <v>0.4286</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1158</v>
+        <v>0.4993</v>
       </c>
       <c r="J23" t="n">
-        <v>0.492</v>
+        <v>0.0169</v>
       </c>
       <c r="K23" t="n">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="L23" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3762</v>
+        <v>0.5162</v>
       </c>
       <c r="N23" t="n">
-        <v>257</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2211</v>
+        <v>0.4193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1096</v>
+        <v>0.2079</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5382</v>
+        <v>-0.4333</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2211</v>
+        <v>0.4193</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3501</v>
+        <v>0.4179</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.129</v>
+        <v>0.0014</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3501</v>
+        <v>0.4179</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4459</v>
+        <v>0.4287</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.129</v>
+        <v>0.0014</v>
       </c>
       <c r="K24" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="L24" t="n">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3169</v>
+        <v>0.4301</v>
       </c>
       <c r="N24" t="n">
-        <v>398</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1643</v>
+        <v>0.1549</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0815</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5638</v>
+        <v>-0.5537</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1643</v>
+        <v>0.1549</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2015</v>
+        <v>-0.2278</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3658</v>
+        <v>0.3827</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2015</v>
+        <v>-0.2278</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2098</v>
+        <v>-0.2337</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3658</v>
+        <v>0.3827</v>
       </c>
       <c r="K25" t="n">
         <v>89</v>
@@ -1587,7 +1587,7 @@
         <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>0.156</v>
+        <v>0.149</v>
       </c>
       <c r="N25" t="n">
         <v>173</v>
@@ -1596,35 +1596,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.122</v>
+        <v>0.1208</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0605</v>
+        <v>0.0599</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5829</v>
+        <v>-0.5692</v>
       </c>
       <c r="E26" t="n">
-        <v>0.122</v>
+        <v>0.1208</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0552</v>
+        <v>0.0799</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0668</v>
+        <v>0.0409</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0552</v>
+        <v>0.0799</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0575</v>
+        <v>0.082</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0668</v>
+        <v>0.0409</v>
       </c>
       <c r="K26" t="n">
         <v>89</v>
@@ -1633,7 +1633,7 @@
         <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1243</v>
+        <v>0.1229</v>
       </c>
       <c r="N26" t="n">
         <v>173</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1065</v>
+        <v>0.1017</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0528</v>
+        <v>0.0504</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5899</v>
+        <v>-0.5779</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1065</v>
+        <v>0.1017</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0726</v>
+        <v>0.0235</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0339</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0726</v>
+        <v>0.0235</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0756</v>
+        <v>0.0241</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0339</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>89</v>
@@ -1679,7 +1679,7 @@
         <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1095</v>
+        <v>0.1023</v>
       </c>
       <c r="N27" t="n">
         <v>173</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0603</v>
+        <v>0.0594</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0299</v>
+        <v>0.0295</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6108</v>
+        <v>-0.5972</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0603</v>
+        <v>0.0594</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0053</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0711</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0053</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>89</v>
@@ -1725,7 +1725,7 @@
         <v>96</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0658</v>
+        <v>0.063</v>
       </c>
       <c r="N28" t="n">
         <v>185</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0844</v>
+        <v>-0.1527</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0419</v>
+        <v>-0.0757</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6761</v>
+        <v>-0.6937</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0844</v>
+        <v>-0.1527</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2732</v>
+        <v>0.2401</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3576</v>
+        <v>-0.3928</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2732</v>
+        <v>0.2401</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2732</v>
+        <v>0.2401</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3576</v>
+        <v>-0.3928</v>
       </c>
       <c r="K29" t="n">
         <v>56</v>
@@ -1771,7 +1771,7 @@
         <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.08439999999999998</v>
+        <v>-0.1527</v>
       </c>
       <c r="N29" t="n">
         <v>109</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.154</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.047</v>
+        <v>-0.0764</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6808</v>
+        <v>-0.6943</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.154</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0927</v>
+        <v>0.067</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1874</v>
+        <v>-0.221</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0927</v>
+        <v>0.067</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0927</v>
+        <v>0.067</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1874</v>
+        <v>-0.221</v>
       </c>
       <c r="K30" t="n">
         <v>56</v>
@@ -1817,7 +1817,7 @@
         <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.154</v>
       </c>
       <c r="N30" t="n">
         <v>109</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2802</v>
+        <v>-0.2832</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1389</v>
+        <v>-0.1404</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7645</v>
+        <v>-0.7531</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2802</v>
+        <v>-0.2832</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2227</v>
+        <v>0.2464</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5029</v>
+        <v>-0.5296</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2227</v>
+        <v>0.2464</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2414</v>
+        <v>0.2593</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5029</v>
+        <v>-0.5296</v>
       </c>
       <c r="K31" t="n">
         <v>89</v>
@@ -1863,7 +1863,7 @@
         <v>96</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2615</v>
+        <v>-0.2703</v>
       </c>
       <c r="N31" t="n">
         <v>185</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.384</v>
+        <v>-0.3803</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1904</v>
+        <v>-0.1886</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8114</v>
+        <v>-0.7973</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.384</v>
+        <v>-0.3803</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0421</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.4261</v>
+        <v>-0.3803</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0421</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1296</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.4261</v>
+        <v>-0.3803</v>
       </c>
       <c r="K32" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2965</v>
+        <v>-0.3803</v>
       </c>
       <c r="N32" t="n">
-        <v>185</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4007</v>
+        <v>-0.4385</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1987</v>
+        <v>-0.2174</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8189</v>
+        <v>-0.8238</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4007</v>
+        <v>-0.4385</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.0134</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4007</v>
+        <v>-1.4519</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.0134</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4007</v>
+        <v>-1.4519</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L33" t="n">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4007</v>
+        <v>-0.3855999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.7905</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3832</v>
+        <v>-0.392</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9868</v>
+        <v>-0.9841</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.7905</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7241</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0486</v>
+        <v>-0.036</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7241</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7241</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0486</v>
+        <v>-0.036</v>
       </c>
       <c r="K34" t="n">
         <v>56</v>
@@ -2001,7 +2001,7 @@
         <v>53</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7726999999999999</v>
+        <v>-0.7905</v>
       </c>
       <c r="N34" t="n">
         <v>109</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8582</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4256</v>
+        <v>-0.4581</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0254</v>
+        <v>-1.0448</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8582</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6283</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2639</v>
+        <v>-0.2956</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6283</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6283</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2639</v>
+        <v>-0.2956</v>
       </c>
       <c r="K35" t="n">
         <v>56</v>
@@ -2047,7 +2047,7 @@
         <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8582000000000001</v>
+        <v>-0.9238999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>109</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3295</v>
+        <v>-1.2807</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6593</v>
+        <v>-0.6351</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2382</v>
+        <v>-1.2072</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3295</v>
+        <v>-1.2807</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3278</v>
+        <v>-0.334</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.0017</v>
+        <v>-0.9467</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3278</v>
+        <v>-0.334</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3278</v>
+        <v>-0.334</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.0017</v>
+        <v>-0.9467</v>
       </c>
       <c r="K36" t="n">
         <v>53</v>
@@ -2093,7 +2093,7 @@
         <v>204</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3295</v>
+        <v>-1.2807</v>
       </c>
       <c r="N36" t="n">
         <v>257</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4339</v>
+        <v>-1.4912</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.711</v>
+        <v>-0.7395</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2853</v>
+        <v>-1.303</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4339</v>
+        <v>-1.4912</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6832</v>
+        <v>-0.7126</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7507</v>
+        <v>-0.7786</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6832</v>
+        <v>-0.7126</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6832</v>
+        <v>-0.7126</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7507</v>
+        <v>-0.7786</v>
       </c>
       <c r="K37" t="n">
         <v>56</v>
@@ -2139,7 +2139,7 @@
         <v>53</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4339</v>
+        <v>-1.4912</v>
       </c>
       <c r="N37" t="n">
         <v>109</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5916</v>
+        <v>-1.6293</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7893</v>
+        <v>-0.8079</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3565</v>
+        <v>-1.3659</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5916</v>
+        <v>-1.6293</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0862</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.5054</v>
+        <v>-1.6293</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0862</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0934</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.5054</v>
+        <v>-1.6293</v>
       </c>
       <c r="K38" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5988</v>
+        <v>-1.6293</v>
       </c>
       <c r="N38" t="n">
-        <v>185</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6251</v>
+        <v>-1.6512</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.8188</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3717</v>
+        <v>-1.3759</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6251</v>
+        <v>-1.6512</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.6251</v>
+        <v>-1.5604</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6251</v>
+        <v>-1.5604</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L39" t="n">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6251</v>
+        <v>-1.6559</v>
       </c>
       <c r="N39" t="n">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2546</v>
+        <v>-2.2006</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.118</v>
+        <v>-1.0912</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6559</v>
+        <v>-1.626</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2546</v>
+        <v>-2.2006</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5251</v>
+        <v>-1.5655</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7295</v>
+        <v>-0.6351</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5251</v>
+        <v>-1.5655</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5251</v>
+        <v>-1.5655</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7295</v>
+        <v>-0.6351</v>
       </c>
       <c r="K40" t="n">
         <v>114</v>
@@ -2277,7 +2277,7 @@
         <v>97</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.2546</v>
+        <v>-2.2006</v>
       </c>
       <c r="N40" t="n">
         <v>211</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4026</v>
+        <v>-2.4298</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1914</v>
+        <v>-1.2049</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7227</v>
+        <v>-1.7303</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4026</v>
+        <v>-2.4298</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.4026</v>
+        <v>-2.4298</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.4026</v>
+        <v>-2.4298</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>230</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4026</v>
+        <v>-2.4298</v>
       </c>
       <c r="N41" t="n">
         <v>230</v>
@@ -2429,10 +2429,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6631</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>17.9037</v>
+        <v>17.8416</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2597</v>
+        <v>0.2769</v>
       </c>
       <c r="J3" t="n">
-        <v>7.0119</v>
+        <v>7.4763</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2227</v>
+        <v>0.24</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0129</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2098</v>
+        <v>0.2272</v>
       </c>
       <c r="J5" t="n">
-        <v>5.6646</v>
+        <v>6.1344</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2061</v>
+        <v>-0.2157</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.5647</v>
+        <v>-5.8239</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5062</v>
+        <v>0.4889</v>
       </c>
       <c r="J7" t="n">
-        <v>13.6674</v>
+        <v>13.2003</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0151</v>
+        <v>-0.0267</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4077</v>
+        <v>-0.7209</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.258</v>
+        <v>-0.2753</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.966</v>
+        <v>-7.4331</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3061</v>
+        <v>-0.3223</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.264699999999999</v>
+        <v>-8.7021</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5476</v>
+        <v>-0.552</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.7852</v>
+        <v>-14.904</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01</v>
+        <v>-0.0052</v>
       </c>
       <c r="J12" t="n">
-        <v>0.27</v>
+        <v>-0.1404</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.011</v>
+        <v>-0.0235</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.297</v>
+        <v>-0.6345</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2265</v>
+        <v>-0.2448</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1155</v>
+        <v>-6.6096</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2457</v>
+        <v>-0.2639</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6339</v>
+        <v>-7.1253</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4534</v>
+        <v>-0.4638</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.2418</v>
+        <v>-12.5226</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.74</v>
       </c>
       <c r="I17" t="n">
-        <v>1.425</v>
+        <v>1.5397</v>
       </c>
       <c r="J17" t="n">
-        <v>38.475</v>
+        <v>41.5719</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.51</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1416</v>
+        <v>1.1431</v>
       </c>
       <c r="J18" t="n">
-        <v>30.8232</v>
+        <v>30.8637</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2612</v>
+        <v>0.2749</v>
       </c>
       <c r="J19" t="n">
-        <v>7.0524</v>
+        <v>7.4223</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.158</v>
+        <v>-0.1442</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.266</v>
+        <v>-3.8934</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2637</v>
+        <v>-0.2466</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.1199</v>
+        <v>-6.6582</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.176</v>
+        <v>-0.2015</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.872</v>
+        <v>-4.433</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2995</v>
+        <v>-0.321</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.589</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3273</v>
+        <v>-0.3478</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.2006</v>
+        <v>-7.6516</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.55</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.394</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.53</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4457</v>
+        <v>-0.4607</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.805400000000001</v>
+        <v>-10.1354</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5928</v>
+        <v>1.7316</v>
       </c>
       <c r="J27" t="n">
-        <v>35.0416</v>
+        <v>38.0952</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.48</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0779</v>
+        <v>1.0575</v>
       </c>
       <c r="J28" t="n">
-        <v>23.7138</v>
+        <v>23.265</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.41</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9818</v>
+        <v>0.9335</v>
       </c>
       <c r="J29" t="n">
-        <v>21.5996</v>
+        <v>20.537</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3894</v>
+        <v>0.4005</v>
       </c>
       <c r="J30" t="n">
-        <v>8.566800000000001</v>
+        <v>8.811</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.12</v>
       </c>
       <c r="I31" t="n">
-        <v>0.309</v>
+        <v>0.3272</v>
       </c>
       <c r="J31" t="n">
-        <v>6.798</v>
+        <v>7.1984</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1152</v>
+        <v>0.1169</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2256</v>
+        <v>3.2732</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0895</v>
       </c>
       <c r="J33" t="n">
-        <v>2.4752</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1245</v>
+        <v>-0.1395</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.486</v>
+        <v>-3.906</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1561</v>
+        <v>-0.1719</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.3708</v>
+        <v>-4.8132</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3247</v>
+        <v>-0.3386</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.0916</v>
+        <v>-9.4808</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0006</v>
+        <v>0.9448</v>
       </c>
       <c r="J37" t="n">
-        <v>28.0168</v>
+        <v>26.4544</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6968</v>
+        <v>0.6684</v>
       </c>
       <c r="J38" t="n">
-        <v>19.5104</v>
+        <v>18.7152</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6505</v>
+        <v>0.6271</v>
       </c>
       <c r="J39" t="n">
-        <v>18.214</v>
+        <v>17.5588</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.24</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6505</v>
+        <v>0.6271</v>
       </c>
       <c r="J40" t="n">
-        <v>18.214</v>
+        <v>17.5588</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2549</v>
+        <v>-0.2404</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.1372</v>
+        <v>-6.7312</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1585</v>
+        <v>-0.1877</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.3285</v>
+        <v>-3.9417</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2878</v>
+        <v>-0.312</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.0438</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.6</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3734</v>
+        <v>-0.3937</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.8414</v>
+        <v>-8.2677</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4642</v>
+        <v>-0.4795</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.748200000000001</v>
+        <v>-10.0695</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5784</v>
+        <v>-0.5854</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1464</v>
+        <v>-12.2934</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.73</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3668</v>
+        <v>1.3547</v>
       </c>
       <c r="J47" t="n">
-        <v>28.7028</v>
+        <v>28.4487</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0975</v>
+        <v>1.0655</v>
       </c>
       <c r="J48" t="n">
-        <v>23.0475</v>
+        <v>22.3755</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.49</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0857</v>
+        <v>1.0521</v>
       </c>
       <c r="J49" t="n">
-        <v>22.7997</v>
+        <v>22.0941</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.48</v>
       </c>
       <c r="I50" t="n">
-        <v>1.0739</v>
+        <v>1.0384</v>
       </c>
       <c r="J50" t="n">
-        <v>22.5519</v>
+        <v>21.8064</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1869</v>
+        <v>0.2162</v>
       </c>
       <c r="J51" t="n">
-        <v>3.9249</v>
+        <v>4.5402</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9953</v>
+        <v>0.9366</v>
       </c>
       <c r="J52" t="n">
-        <v>25.8778</v>
+        <v>24.3516</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6123</v>
+        <v>0.5911</v>
       </c>
       <c r="J53" t="n">
-        <v>15.9198</v>
+        <v>15.3686</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.492</v>
+        <v>0.4824</v>
       </c>
       <c r="J54" t="n">
-        <v>12.792</v>
+        <v>12.5424</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3636</v>
+        <v>0.3651</v>
       </c>
       <c r="J55" t="n">
-        <v>9.4536</v>
+        <v>9.492599999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1754</v>
+        <v>-0.1669</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.5604</v>
+        <v>-4.3394</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.22</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4868</v>
       </c>
       <c r="J57" t="n">
-        <v>13.039</v>
+        <v>12.6568</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2667</v>
+        <v>0.2673</v>
       </c>
       <c r="J58" t="n">
-        <v>6.9342</v>
+        <v>6.9498</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0576</v>
+        <v>-0.0683</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.4976</v>
+        <v>-1.7758</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.79</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2406</v>
+        <v>-0.2557</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.2556</v>
+        <v>-6.6482</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.44</v>
+        <v>-0.4487</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.44</v>
+        <v>-11.6662</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.92</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6615</v>
+        <v>1.6527</v>
       </c>
       <c r="J62" t="n">
-        <v>44.8605</v>
+        <v>44.6229</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9302</v>
+        <v>0.8734</v>
       </c>
       <c r="J63" t="n">
-        <v>25.1154</v>
+        <v>23.5818</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3034</v>
+        <v>0.3109</v>
       </c>
       <c r="J64" t="n">
-        <v>8.191800000000001</v>
+        <v>8.394299999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.515</v>
+        <v>-0.482</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.905</v>
+        <v>-13.014</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8257</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.2939</v>
+        <v>-20.4822</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2293</v>
+        <v>0.2302</v>
       </c>
       <c r="J67" t="n">
-        <v>6.1911</v>
+        <v>6.2154</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1122</v>
+        <v>0.1147</v>
       </c>
       <c r="J68" t="n">
-        <v>3.0294</v>
+        <v>3.0969</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0169</v>
+        <v>0.0121</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4563</v>
+        <v>0.3267</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2085</v>
+        <v>-0.2244</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.6295</v>
+        <v>-6.0588</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3825</v>
+        <v>-0.3941</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3275</v>
+        <v>-10.6407</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7096</v>
       </c>
       <c r="J72" t="n">
-        <v>21.5586</v>
+        <v>20.5784</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6509</v>
+        <v>0.6274</v>
       </c>
       <c r="J73" t="n">
-        <v>18.8761</v>
+        <v>18.1946</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6509</v>
+        <v>0.6274</v>
       </c>
       <c r="J74" t="n">
-        <v>18.8761</v>
+        <v>18.1946</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6046</v>
+        <v>0.5859</v>
       </c>
       <c r="J75" t="n">
-        <v>17.5334</v>
+        <v>16.9911</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2988</v>
+        <v>0.3076</v>
       </c>
       <c r="J76" t="n">
-        <v>8.6652</v>
+        <v>8.920400000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.55</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0655</v>
+        <v>1.0176</v>
       </c>
       <c r="J77" t="n">
-        <v>30.8995</v>
+        <v>29.5104</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.8</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.4989</v>
+        <v>-6.9832</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.4989</v>
+        <v>-6.9832</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2439</v>
+        <v>-0.2604</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.0731</v>
+        <v>-7.5516</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.46</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5432</v>
+        <v>-0.5472</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.7528</v>
+        <v>-15.8688</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6948</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>25.0128</v>
+        <v>23.6808</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3012</v>
+        <v>0.3024</v>
       </c>
       <c r="J83" t="n">
-        <v>10.8432</v>
+        <v>10.8864</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2438</v>
+        <v>0.2485</v>
       </c>
       <c r="J84" t="n">
-        <v>8.7768</v>
+        <v>8.946</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1839</v>
+        <v>0.1912</v>
       </c>
       <c r="J85" t="n">
-        <v>6.6204</v>
+        <v>6.8832</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4249</v>
+        <v>-0.4073</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.2964</v>
+        <v>-14.6628</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.24</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5162</v>
+        <v>0.5043</v>
       </c>
       <c r="J87" t="n">
-        <v>18.5832</v>
+        <v>18.1548</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3102</v>
+        <v>0.3125</v>
       </c>
       <c r="J88" t="n">
-        <v>11.1672</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
       <c r="J89" t="n">
-        <v>2.4624</v>
+        <v>2.7036</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2474</v>
+        <v>-0.261</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.9064</v>
+        <v>-9.396000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2867</v>
+        <v>-0.2997</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.3212</v>
+        <v>-10.7892</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4026</v>
+        <v>0.4295</v>
       </c>
       <c r="J92" t="n">
-        <v>10.065</v>
+        <v>10.7375</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0568</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.42</v>
+        <v>-1.785</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1703</v>
+        <v>-0.1879</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.2575</v>
+        <v>-4.6975</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2383</v>
+        <v>-0.256</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.9575</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5745</v>
+        <v>-0.5772</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.3625</v>
+        <v>-14.43</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6448</v>
+        <v>0.7153</v>
       </c>
       <c r="J97" t="n">
-        <v>16.12</v>
+        <v>17.8825</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.23</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5085</v>
+        <v>0.5641</v>
       </c>
       <c r="J98" t="n">
-        <v>12.7125</v>
+        <v>14.1025</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.22</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4947</v>
+        <v>0.5485</v>
       </c>
       <c r="J99" t="n">
-        <v>12.3675</v>
+        <v>13.7125</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.439</v>
+        <v>0.4852</v>
       </c>
       <c r="J100" t="n">
-        <v>10.975</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1518</v>
+        <v>0.1691</v>
       </c>
       <c r="J101" t="n">
-        <v>3.795</v>
+        <v>4.2275</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5414</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
-        <v>15.7006</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5104</v>
+        <v>0.5649</v>
       </c>
       <c r="J103" t="n">
-        <v>14.8016</v>
+        <v>16.3821</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2242</v>
+        <v>-0.2388</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.5018</v>
+        <v>-6.9252</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3316</v>
+        <v>-0.344</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.616400000000001</v>
+        <v>-9.976000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3693</v>
+        <v>-0.3805</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.7097</v>
+        <v>-11.0345</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6227</v>
+        <v>0.6867</v>
       </c>
       <c r="J107" t="n">
-        <v>18.0583</v>
+        <v>19.9143</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3891</v>
+        <v>0.42</v>
       </c>
       <c r="J108" t="n">
-        <v>11.2839</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3207</v>
+        <v>0.3236</v>
       </c>
       <c r="J109" t="n">
-        <v>9.3003</v>
+        <v>9.384399999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0298</v>
+        <v>0.0426</v>
       </c>
       <c r="J110" t="n">
-        <v>0.8642</v>
+        <v>1.2354</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0798</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.3142</v>
+        <v>-2.2272</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5216</v>
+        <v>0.5649</v>
       </c>
       <c r="J112" t="n">
-        <v>15.648</v>
+        <v>16.947</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3918</v>
+        <v>0.4119</v>
       </c>
       <c r="J113" t="n">
-        <v>11.754</v>
+        <v>12.357</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1494</v>
+        <v>0.1488</v>
       </c>
       <c r="J114" t="n">
-        <v>4.482</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6018</v>
+        <v>-0.5739</v>
       </c>
       <c r="J115" t="n">
-        <v>-18.054</v>
+        <v>-17.217</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.2404</v>
+        <v>-1.1265</v>
       </c>
       <c r="J116" t="n">
-        <v>-37.212</v>
+        <v>-33.795</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.04</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1481</v>
+        <v>1.2759</v>
       </c>
       <c r="J117" t="n">
-        <v>34.443</v>
+        <v>38.277</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1221</v>
+        <v>0.1357</v>
       </c>
       <c r="J118" t="n">
-        <v>3.663</v>
+        <v>4.071</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0485</v>
+        <v>0.0609</v>
       </c>
       <c r="J119" t="n">
-        <v>1.455</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2715</v>
+        <v>-0.2819</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.145</v>
+        <v>-8.457000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3576</v>
+        <v>-0.3662</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.728</v>
+        <v>-10.986</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4483</v>
+        <v>0.4997</v>
       </c>
       <c r="J122" t="n">
-        <v>18.3803</v>
+        <v>20.4877</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3365</v>
+        <v>0.347</v>
       </c>
       <c r="J123" t="n">
-        <v>13.7965</v>
+        <v>14.227</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1189</v>
+        <v>0.1297</v>
       </c>
       <c r="J124" t="n">
-        <v>4.8749</v>
+        <v>5.3177</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1813</v>
+        <v>-0.1939</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.4333</v>
+        <v>-7.9499</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3494</v>
+        <v>-0.3598</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.3254</v>
+        <v>-14.7518</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2497</v>
+        <v>0.2633</v>
       </c>
       <c r="J127" t="n">
-        <v>10.2377</v>
+        <v>10.7953</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1676</v>
+        <v>0.1817</v>
       </c>
       <c r="J128" t="n">
-        <v>6.8716</v>
+        <v>7.4497</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1241</v>
+        <v>0.1374</v>
       </c>
       <c r="J129" t="n">
-        <v>5.0881</v>
+        <v>5.6334</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1058</v>
       </c>
       <c r="J130" t="n">
-        <v>3.8417</v>
+        <v>4.3378</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1725</v>
+        <v>-0.1846</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.0725</v>
+        <v>-7.5686</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.21</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6287</v>
+        <v>1.7686</v>
       </c>
       <c r="J132" t="n">
-        <v>32.574</v>
+        <v>35.372</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.86</v>
       </c>
       <c r="I133" t="n">
-        <v>1.2394</v>
+        <v>1.3625</v>
       </c>
       <c r="J133" t="n">
-        <v>24.788</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5477</v>
+        <v>0.6153</v>
       </c>
       <c r="J134" t="n">
-        <v>10.954</v>
+        <v>12.306</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3908</v>
+        <v>0.4368</v>
       </c>
       <c r="J135" t="n">
-        <v>7.816</v>
+        <v>8.736000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6781</v>
+        <v>-0.6178</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.562</v>
+        <v>-12.356</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.82</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1461</v>
+        <v>-0.1758</v>
       </c>
       <c r="J137" t="n">
-        <v>-2.922</v>
+        <v>-3.516</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.7</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2771</v>
+        <v>-0.3018</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.542</v>
+        <v>-6.036</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.59</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3815</v>
+        <v>-0.4015</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.63</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4544</v>
+        <v>-0.4704</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.087999999999999</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.35</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6069</v>
+        <v>-0.6116</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.138</v>
+        <v>-12.232</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4101</v>
+        <v>0.4439</v>
       </c>
       <c r="J142" t="n">
-        <v>10.6626</v>
+        <v>11.5414</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0653</v>
+        <v>-0.078</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.6978</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.87</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1545</v>
+        <v>-0.1707</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.017</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2939</v>
+        <v>-0.3091</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.6414</v>
+        <v>-8.0366</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.387600000000001</v>
+        <v>-8.762</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8119</v>
       </c>
       <c r="J147" t="n">
-        <v>19.1204</v>
+        <v>21.1094</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8119</v>
       </c>
       <c r="J148" t="n">
-        <v>19.1204</v>
+        <v>21.1094</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4434</v>
+        <v>0.489</v>
       </c>
       <c r="J149" t="n">
-        <v>11.5284</v>
+        <v>12.714</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.04</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1312</v>
+        <v>0.1461</v>
       </c>
       <c r="J150" t="n">
-        <v>3.4112</v>
+        <v>3.7986</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7654</v>
+        <v>-0.7073</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.9004</v>
+        <v>-18.3898</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.13</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3372</v>
+        <v>0.3362</v>
       </c>
       <c r="J152" t="n">
-        <v>9.7788</v>
+        <v>9.7498</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3207</v>
+        <v>0.3169</v>
       </c>
       <c r="J153" t="n">
-        <v>9.3003</v>
+        <v>9.190099999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1856</v>
+        <v>-0.2021</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.3824</v>
+        <v>-5.8609</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2653</v>
+        <v>-0.281</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.6937</v>
+        <v>-8.148999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4077</v>
+        <v>-0.4187</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.8233</v>
+        <v>-12.1423</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.64</v>
+        <v>0.708</v>
       </c>
       <c r="J157" t="n">
-        <v>18.56</v>
+        <v>20.532</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5147</v>
+        <v>0.5694</v>
       </c>
       <c r="J158" t="n">
-        <v>14.9263</v>
+        <v>16.5126</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.443</v>
+        <v>0.4886</v>
       </c>
       <c r="J159" t="n">
-        <v>12.847</v>
+        <v>14.1694</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3995</v>
+        <v>0.4362</v>
       </c>
       <c r="J160" t="n">
-        <v>11.5855</v>
+        <v>12.6498</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3922</v>
+        <v>-0.3722</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.3738</v>
+        <v>-10.7938</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="J162" t="n">
-        <v>0.822</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0373</v>
+        <v>-0.0485</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.119</v>
+        <v>-1.455</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1225</v>
+        <v>-0.138</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.675</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2537</v>
+        <v>-0.27</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.611</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2732</v>
+        <v>-0.2891</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.196</v>
+        <v>-8.673</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7921</v>
+        <v>0.8752</v>
       </c>
       <c r="J167" t="n">
-        <v>23.763</v>
+        <v>26.256</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4399</v>
+        <v>0.4861</v>
       </c>
       <c r="J168" t="n">
-        <v>13.197</v>
+        <v>14.583</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4255</v>
+        <v>0.4695</v>
       </c>
       <c r="J169" t="n">
-        <v>12.765</v>
+        <v>14.085</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3292</v>
+        <v>0.3373</v>
       </c>
       <c r="J170" t="n">
-        <v>9.875999999999999</v>
+        <v>10.119</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1861</v>
+        <v>0.201</v>
       </c>
       <c r="J171" t="n">
-        <v>5.583</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2993</v>
+        <v>0.3123</v>
       </c>
       <c r="J172" t="n">
-        <v>8.6797</v>
+        <v>9.056699999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2474</v>
+        <v>0.2616</v>
       </c>
       <c r="J173" t="n">
-        <v>7.1746</v>
+        <v>7.5864</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2208</v>
+        <v>0.2353</v>
       </c>
       <c r="J174" t="n">
-        <v>6.4032</v>
+        <v>6.8237</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.042</v>
+        <v>-0.0473</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.218</v>
+        <v>-1.3717</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2056</v>
+        <v>-0.2175</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.9624</v>
+        <v>-6.3075</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3995</v>
+        <v>0.4414</v>
       </c>
       <c r="J177" t="n">
-        <v>11.5855</v>
+        <v>12.8006</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3522</v>
+        <v>0.3699</v>
       </c>
       <c r="J178" t="n">
-        <v>10.2138</v>
+        <v>10.7271</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1331</v>
+        <v>0.1447</v>
       </c>
       <c r="J179" t="n">
-        <v>3.8599</v>
+        <v>4.1963</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="J180" t="n">
-        <v>1.8879</v>
+        <v>2.1634</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.64</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3978</v>
+        <v>-0.4062</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.5362</v>
+        <v>-11.7798</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.74</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1847</v>
+        <v>-0.2219</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.3246</v>
+        <v>-3.9942</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.6</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3428</v>
+        <v>-0.3699</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.1704</v>
+        <v>-6.6582</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.45</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4868</v>
+        <v>-0.5043</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.7624</v>
+        <v>-9.077400000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.32</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6139</v>
+        <v>-0.6208</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.0502</v>
+        <v>-11.1744</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6442</v>
+        <v>-0.6484</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.5956</v>
+        <v>-11.6712</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4602</v>
+        <v>1.5994</v>
       </c>
       <c r="J187" t="n">
-        <v>26.2836</v>
+        <v>28.7892</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.88</v>
       </c>
       <c r="I188" t="n">
-        <v>1.2328</v>
+        <v>1.3607</v>
       </c>
       <c r="J188" t="n">
-        <v>22.1904</v>
+        <v>24.4926</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.6</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9247</v>
+        <v>1.0313</v>
       </c>
       <c r="J189" t="n">
-        <v>16.6446</v>
+        <v>18.5634</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.53</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8442</v>
+        <v>0.9442</v>
       </c>
       <c r="J190" t="n">
-        <v>15.1956</v>
+        <v>16.9956</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.06</v>
       </c>
       <c r="I191" t="n">
-        <v>0.093</v>
+        <v>0.1358</v>
       </c>
       <c r="J191" t="n">
-        <v>1.674</v>
+        <v>2.4444</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.22</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5926</v>
+        <v>0.5542</v>
       </c>
       <c r="J192" t="n">
-        <v>14.2224</v>
+        <v>13.3008</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.6344</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3622</v>
+        <v>-0.3782</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.6928</v>
+        <v>-9.0768</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4184</v>
+        <v>-0.4317</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.0416</v>
+        <v>-10.3608</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5365</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.7128</v>
+        <v>-12.876</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.09</v>
+        <v>1.0505</v>
       </c>
       <c r="J197" t="n">
-        <v>26.16</v>
+        <v>25.212</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0645</v>
+        <v>1.0206</v>
       </c>
       <c r="J198" t="n">
-        <v>25.548</v>
+        <v>24.4944</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.26</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6899</v>
+        <v>0.6637</v>
       </c>
       <c r="J199" t="n">
-        <v>16.5576</v>
+        <v>15.9288</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3165</v>
+        <v>0.3263</v>
       </c>
       <c r="J200" t="n">
-        <v>7.596</v>
+        <v>7.8312</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.2016</v>
+        <v>0.3816</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6385</v>
+        <v>0.6347</v>
       </c>
       <c r="J202" t="n">
-        <v>19.155</v>
+        <v>19.041</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2036</v>
+        <v>0.2192</v>
       </c>
       <c r="J203" t="n">
-        <v>6.108</v>
+        <v>6.576</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1493</v>
+        <v>0.1643</v>
       </c>
       <c r="J204" t="n">
-        <v>4.479</v>
+        <v>4.929</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1554</v>
+        <v>-0.1661</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.662</v>
+        <v>-4.983</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1877</v>
+        <v>-0.1989</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.631</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5612</v>
+        <v>0.5485</v>
       </c>
       <c r="J207" t="n">
-        <v>16.836</v>
+        <v>16.455</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.97</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0478</v>
+        <v>-0.0565</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.434</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1634</v>
+        <v>-0.1775</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.902</v>
+        <v>-5.325</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.84</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1948</v>
+        <v>-0.2092</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.844</v>
+        <v>-6.276</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.762</v>
+        <v>-7.191</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4017</v>
+        <v>0.3993</v>
       </c>
       <c r="J212" t="n">
-        <v>14.0595</v>
+        <v>13.9755</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.364</v>
+        <v>0.3641</v>
       </c>
       <c r="J213" t="n">
-        <v>12.74</v>
+        <v>12.7435</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.066</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>2.31</v>
+        <v>2.569</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2188</v>
+        <v>-0.2324</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.658</v>
+        <v>-8.134</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.82</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2188</v>
+        <v>-0.2324</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.658</v>
+        <v>-8.134</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0385</v>
+        <v>0.9797</v>
       </c>
       <c r="J217" t="n">
-        <v>36.3475</v>
+        <v>34.2895</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>1.023</v>
+        <v>0.9615</v>
       </c>
       <c r="J218" t="n">
-        <v>35.805</v>
+        <v>33.6525</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.09</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2976</v>
+        <v>0.2999</v>
       </c>
       <c r="J219" t="n">
-        <v>10.416</v>
+        <v>10.4965</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6199</v>
+        <v>-0.5817</v>
       </c>
       <c r="J220" t="n">
-        <v>-21.6965</v>
+        <v>-20.3595</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7986</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-27.951</v>
+        <v>-25.879</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.92</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6042</v>
+        <v>1.6017</v>
       </c>
       <c r="J222" t="n">
-        <v>35.2924</v>
+        <v>35.2374</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1445</v>
+        <v>1.1143</v>
       </c>
       <c r="J223" t="n">
-        <v>25.179</v>
+        <v>24.5146</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.26</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="J224" t="n">
-        <v>14.7378</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.526</v>
+        <v>0.5218</v>
       </c>
       <c r="J225" t="n">
-        <v>11.572</v>
+        <v>11.4796</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2903</v>
+        <v>-0.2653</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.3866</v>
+        <v>-5.8366</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.88</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1194</v>
+        <v>-0.141</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.6268</v>
+        <v>-3.102</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1748</v>
+        <v>-0.1961</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.8456</v>
+        <v>-4.3142</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2362</v>
+        <v>-0.2566</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.1964</v>
+        <v>-5.6452</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.366</v>
+        <v>-0.3828</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.052</v>
+        <v>-8.4216</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.54</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4502</v>
+        <v>-0.4627</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.904400000000001</v>
+        <v>-10.1794</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1762</v>
+        <v>1.1422</v>
       </c>
       <c r="J232" t="n">
-        <v>39.9908</v>
+        <v>38.8348</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7504</v>
       </c>
       <c r="J233" t="n">
-        <v>26.8532</v>
+        <v>25.5136</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5344</v>
+        <v>0.5224</v>
       </c>
       <c r="J234" t="n">
-        <v>18.1696</v>
+        <v>17.7616</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5099</v>
+        <v>0.5003</v>
       </c>
       <c r="J235" t="n">
-        <v>17.3366</v>
+        <v>17.0102</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4918</v>
+        <v>-0.4601</v>
       </c>
       <c r="J236" t="n">
-        <v>-16.7212</v>
+        <v>-15.6434</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3926</v>
+        <v>0.3811</v>
       </c>
       <c r="J237" t="n">
-        <v>13.3484</v>
+        <v>12.9574</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2675</v>
+        <v>0.2631</v>
       </c>
       <c r="J238" t="n">
-        <v>9.095000000000001</v>
+        <v>8.945399999999999</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.233</v>
+        <v>-0.2499</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.922</v>
+        <v>-8.496600000000001</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.66</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3581</v>
+        <v>-0.3717</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.1754</v>
+        <v>-12.6378</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3581</v>
+        <v>-0.3717</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.1754</v>
+        <v>-12.6378</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.01</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4305</v>
+        <v>1.5592</v>
       </c>
       <c r="J242" t="n">
-        <v>28.61</v>
+        <v>31.184</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I243" t="n">
-        <v>1.3278</v>
+        <v>1.4521</v>
       </c>
       <c r="J243" t="n">
-        <v>26.556</v>
+        <v>29.042</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.09</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2319</v>
+        <v>0.2545</v>
       </c>
       <c r="J244" t="n">
-        <v>4.638</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2924</v>
+        <v>-0.2668</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.848</v>
+        <v>-5.336</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3245</v>
+        <v>-0.2972</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.49</v>
+        <v>-5.944</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0345</v>
+        <v>-0.0573</v>
       </c>
       <c r="J247" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.146</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.177</v>
+        <v>-0.2001</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.54</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2088</v>
+        <v>-0.2313</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.176</v>
+        <v>-4.626</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.64</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3507</v>
+        <v>-0.3693</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.014</v>
+        <v>-7.386</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.27</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6962</v>
+        <v>-0.6919</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.924</v>
+        <v>-13.838</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.25</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6765</v>
+        <v>1.8175</v>
       </c>
       <c r="J252" t="n">
-        <v>36.883</v>
+        <v>39.985</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7654</v>
+        <v>0.8546</v>
       </c>
       <c r="J253" t="n">
-        <v>16.8388</v>
+        <v>18.8012</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6419</v>
+        <v>0.719</v>
       </c>
       <c r="J254" t="n">
-        <v>14.1218</v>
+        <v>15.818</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5629</v>
+        <v>0.6317</v>
       </c>
       <c r="J255" t="n">
-        <v>12.3838</v>
+        <v>13.8974</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.37</v>
+        <v>-0.3366</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.140000000000001</v>
+        <v>-7.4052</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0613</v>
+        <v>0.0198</v>
       </c>
       <c r="J257" t="n">
-        <v>1.3486</v>
+        <v>0.4356</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.72</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2739</v>
+        <v>-0.2957</v>
       </c>
       <c r="J258" t="n">
-        <v>-6.0258</v>
+        <v>-6.5054</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.63</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.356</v>
+        <v>-0.3751</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.832</v>
+        <v>-8.2522</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.62</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3651</v>
+        <v>-0.3838</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.0322</v>
+        <v>-8.4436</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5899</v>
+        <v>-0.5945</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.9778</v>
+        <v>-13.079</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.36</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4771</v>
+        <v>0.5286</v>
       </c>
       <c r="J262" t="n">
-        <v>12.8817</v>
+        <v>14.2722</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0624</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J263" t="n">
-        <v>1.6848</v>
+        <v>1.7874</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.86</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1691</v>
+        <v>-0.1845</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.5657</v>
+        <v>-4.9815</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.5914</v>
+        <v>-8.9559</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3372</v>
+        <v>-0.3502</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.1044</v>
+        <v>-9.455399999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2935</v>
+        <v>0.308</v>
       </c>
       <c r="J267" t="n">
-        <v>7.9245</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2809</v>
+        <v>0.2956</v>
       </c>
       <c r="J268" t="n">
-        <v>7.5843</v>
+        <v>7.9812</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.14</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2162</v>
+        <v>0.2318</v>
       </c>
       <c r="J269" t="n">
-        <v>5.8374</v>
+        <v>6.2586</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.06</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1048</v>
+        <v>0.1188</v>
       </c>
       <c r="J270" t="n">
-        <v>2.8296</v>
+        <v>3.2076</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1449</v>
+        <v>-0.1553</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.9123</v>
+        <v>-4.1931</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7982</v>
+        <v>0.8753</v>
       </c>
       <c r="J272" t="n">
-        <v>21.5514</v>
+        <v>23.6331</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3466</v>
+        <v>0.3534</v>
       </c>
       <c r="J273" t="n">
-        <v>9.3582</v>
+        <v>9.5418</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1479</v>
+        <v>-0.1477</v>
       </c>
       <c r="J274" t="n">
-        <v>-3.9933</v>
+        <v>-3.9879</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2161</v>
+        <v>-0.2133</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.8347</v>
+        <v>-5.7591</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3689</v>
+        <v>-0.3559</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.9603</v>
+        <v>-9.609299999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3615</v>
+        <v>0.3801</v>
       </c>
       <c r="J277" t="n">
-        <v>9.7605</v>
+        <v>10.2627</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1146</v>
+        <v>0.1236</v>
       </c>
       <c r="J278" t="n">
-        <v>3.0942</v>
+        <v>3.3372</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0368</v>
+        <v>0.0427</v>
       </c>
       <c r="J279" t="n">
-        <v>0.9936</v>
+        <v>1.1529</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0211</v>
+        <v>-0.0257</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.5697</v>
+        <v>-0.6939</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2096</v>
+        <v>-0.2229</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.6592</v>
+        <v>-6.0183</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.028</v>
+        <v>1.1242</v>
       </c>
       <c r="J282" t="n">
-        <v>30.84</v>
+        <v>33.726</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6035</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J283" t="n">
-        <v>18.105</v>
+        <v>20.004</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5187</v>
+        <v>0.5729</v>
       </c>
       <c r="J284" t="n">
-        <v>15.561</v>
+        <v>17.187</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.7351</v>
+        <v>-0.6815</v>
       </c>
       <c r="J285" t="n">
-        <v>-22.053</v>
+        <v>-20.445</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7604</v>
+        <v>-0.7038</v>
       </c>
       <c r="J286" t="n">
-        <v>-22.812</v>
+        <v>-21.114</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.28</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4891</v>
+        <v>0.5406</v>
       </c>
       <c r="J287" t="n">
-        <v>14.673</v>
+        <v>16.218</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1707</v>
+        <v>0.1766</v>
       </c>
       <c r="J288" t="n">
-        <v>5.121</v>
+        <v>5.298</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I289" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1055</v>
       </c>
       <c r="J289" t="n">
-        <v>2.988</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2838</v>
+        <v>-0.2974</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.513999999999999</v>
+        <v>-8.922000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3413</v>
+        <v>-0.3534</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.239</v>
+        <v>-10.602</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8645</v>
+        <v>0.9517</v>
       </c>
       <c r="J292" t="n">
-        <v>23.3415</v>
+        <v>25.6959</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8385</v>
+        <v>0.9238</v>
       </c>
       <c r="J293" t="n">
-        <v>22.6395</v>
+        <v>24.9426</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1287</v>
+        <v>0.1444</v>
       </c>
       <c r="J294" t="n">
-        <v>3.4749</v>
+        <v>3.8988</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1723</v>
+        <v>-0.1647</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.6521</v>
+        <v>-4.4469</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5606</v>
+        <v>-0.5248</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.1362</v>
+        <v>-14.1696</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.17</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3893</v>
+        <v>0.4141</v>
       </c>
       <c r="J297" t="n">
-        <v>10.5111</v>
+        <v>11.1807</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.96</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0512</v>
+        <v>-0.0634</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.3824</v>
+        <v>-1.7118</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.88</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1437</v>
+        <v>-0.1598</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.8799</v>
+        <v>-4.3146</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.76</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2637</v>
+        <v>-0.2798</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.1199</v>
+        <v>-7.5546</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.63</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3876</v>
+        <v>-0.3997</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.4652</v>
+        <v>-10.7919</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>0.868</v>
+        <v>0.9596</v>
       </c>
       <c r="J302" t="n">
-        <v>22.568</v>
+        <v>24.9496</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6102</v>
+        <v>0.679</v>
       </c>
       <c r="J303" t="n">
-        <v>15.8652</v>
+        <v>17.654</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.27</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5572</v>
+        <v>0.6201</v>
       </c>
       <c r="J304" t="n">
-        <v>14.4872</v>
+        <v>16.1226</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.22</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4902</v>
+        <v>0.5448</v>
       </c>
       <c r="J305" t="n">
-        <v>12.7452</v>
+        <v>14.1648</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2303</v>
+        <v>-0.2147</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.9878</v>
+        <v>-5.5822</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.95</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0437</v>
+        <v>-0.0612</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.1362</v>
+        <v>-1.5912</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.91</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0939</v>
+        <v>-0.113</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.4414</v>
+        <v>-2.938</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2127</v>
+        <v>-0.2322</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.5302</v>
+        <v>-6.0372</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3631</v>
+        <v>-0.3789</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.4406</v>
+        <v>-9.8514</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4379</v>
+        <v>-0.4501</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.3854</v>
+        <v>-11.7026</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.4</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5978</v>
+        <v>0.6665</v>
       </c>
       <c r="J312" t="n">
-        <v>16.1406</v>
+        <v>17.9955</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3025</v>
+        <v>0.3069</v>
       </c>
       <c r="J313" t="n">
-        <v>8.1675</v>
+        <v>8.286300000000001</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.01</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0363</v>
+        <v>0.0424</v>
       </c>
       <c r="J314" t="n">
-        <v>0.9801</v>
+        <v>1.1448</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.84</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2</v>
+        <v>-0.2132</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.4</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3472</v>
+        <v>-0.3581</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.3744</v>
+        <v>-9.668699999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.47</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8478</v>
+        <v>0.9319</v>
       </c>
       <c r="J317" t="n">
-        <v>22.8906</v>
+        <v>25.1613</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6182</v>
+        <v>0.6829</v>
       </c>
       <c r="J318" t="n">
-        <v>16.6914</v>
+        <v>18.4383</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.17</v>
+        <v>0.1818</v>
       </c>
       <c r="J319" t="n">
-        <v>4.59</v>
+        <v>4.9086</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.17</v>
+        <v>0.1818</v>
       </c>
       <c r="J320" t="n">
-        <v>4.59</v>
+        <v>4.9086</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7341</v>
+        <v>-0.6808</v>
       </c>
       <c r="J321" t="n">
-        <v>-19.8207</v>
+        <v>-18.3816</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.43</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4483</v>
+        <v>0.5127</v>
       </c>
       <c r="J322" t="n">
-        <v>10.3109</v>
+        <v>11.7921</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.39</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4229</v>
+        <v>0.4825</v>
       </c>
       <c r="J323" t="n">
-        <v>9.726699999999999</v>
+        <v>11.0975</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.31</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3721</v>
+        <v>0.4145</v>
       </c>
       <c r="J324" t="n">
-        <v>8.558299999999999</v>
+        <v>9.5335</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.26</v>
       </c>
       <c r="I325" t="n">
-        <v>0.337</v>
+        <v>0.3607</v>
       </c>
       <c r="J325" t="n">
-        <v>7.751</v>
+        <v>8.296099999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2704</v>
+        <v>0.2907</v>
       </c>
       <c r="J326" t="n">
-        <v>6.2192</v>
+        <v>6.6861</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.98</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0218</v>
+        <v>-0.0026</v>
       </c>
       <c r="J327" t="n">
-        <v>0.5014</v>
+        <v>-0.0598</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1145</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.1229</v>
+        <v>-2.6335</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.61</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3825</v>
+        <v>-0.3989</v>
       </c>
       <c r="J329" t="n">
-        <v>-8.797499999999999</v>
+        <v>-9.1747</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.6</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3918</v>
+        <v>-0.4078</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.0114</v>
+        <v>-9.3794</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4946</v>
+        <v>-0.5048</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.3758</v>
+        <v>-11.6104</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.91</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0667</v>
+        <v>-0.0916</v>
       </c>
       <c r="J332" t="n">
-        <v>-1.5341</v>
+        <v>-2.1068</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.71</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2847</v>
+        <v>-0.3058</v>
       </c>
       <c r="J333" t="n">
-        <v>-6.5481</v>
+        <v>-7.0334</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2941</v>
+        <v>-0.315</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.7643</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3661</v>
+        <v>-0.3846</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.420299999999999</v>
+        <v>-8.845800000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5532</v>
+        <v>-0.5604</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.7236</v>
+        <v>-12.8892</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.75</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1341</v>
+        <v>1.2478</v>
       </c>
       <c r="J337" t="n">
-        <v>26.0843</v>
+        <v>28.6994</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.49</v>
       </c>
       <c r="I338" t="n">
-        <v>0.8226</v>
+        <v>0.9149</v>
       </c>
       <c r="J338" t="n">
-        <v>18.9198</v>
+        <v>21.0427</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.46</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7859</v>
+        <v>0.875</v>
       </c>
       <c r="J339" t="n">
-        <v>18.0757</v>
+        <v>20.125</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4183</v>
+        <v>0.4672</v>
       </c>
       <c r="J340" t="n">
-        <v>9.620900000000001</v>
+        <v>10.7456</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.96</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2562</v>
+        <v>-0.2328</v>
       </c>
       <c r="J341" t="n">
-        <v>-5.8926</v>
+        <v>-5.3544</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5608/event_5608_evp_summary.xlsx
+++ b/database/event/5608/event_5608_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.898199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.939</v>
+        <v>4.9084</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9098</v>
+        <v>3.9033</v>
       </c>
       <c r="E2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.898199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7692</v>
+        <v>3.6914</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5247</v>
+        <v>5.5095</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4358</v>
+        <v>6.454</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7318</v>
+        <v>6.7387</v>
       </c>
       <c r="K2" t="n">
         <v>158</v>
@@ -529,7 +529,7 @@
         <v>240</v>
       </c>
       <c r="M2" t="n">
-        <v>13.1676</v>
+        <v>13.1927</v>
       </c>
       <c r="N2" t="n">
         <v>398</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5375</v>
+        <v>5.4108</v>
       </c>
       <c r="C3" t="n">
-        <v>2.746</v>
+        <v>2.6831</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8966</v>
+        <v>1.8591</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5375</v>
+        <v>5.4108</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2451</v>
+        <v>1.1429</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2924</v>
+        <v>4.2679</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2451</v>
+        <v>1.1429</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2451</v>
+        <v>1.1429</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2924</v>
+        <v>4.2679</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5375</v>
+        <v>5.4108</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9602</v>
+        <v>4.8368</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4597</v>
+        <v>2.3985</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6338</v>
+        <v>1.5976</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9602</v>
+        <v>4.8368</v>
       </c>
       <c r="F4" t="n">
-        <v>3.684</v>
+        <v>3.6043</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2762</v>
+        <v>1.2325</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3383</v>
+        <v>5.3098</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2187</v>
+        <v>6.2201</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2762</v>
+        <v>1.2325</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>240</v>
       </c>
       <c r="M4" t="n">
-        <v>7.4949</v>
+        <v>7.4526</v>
       </c>
       <c r="N4" t="n">
         <v>398</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8984</v>
+        <v>4.6956</v>
       </c>
       <c r="C5" t="n">
-        <v>2.429</v>
+        <v>2.3285</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6056</v>
+        <v>1.5333</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8984</v>
+        <v>4.6956</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5696</v>
+        <v>2.4898</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3288</v>
+        <v>2.2059</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8992</v>
+        <v>2.7557</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3773</v>
+        <v>3.2281</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3288</v>
+        <v>2.2059</v>
       </c>
       <c r="K5" t="n">
         <v>158</v>
@@ -667,7 +667,7 @@
         <v>240</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7061</v>
+        <v>5.434</v>
       </c>
       <c r="N5" t="n">
         <v>398</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1915</v>
+        <v>4.0387</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0785</v>
+        <v>2.0027</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2839</v>
+        <v>1.234</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1915</v>
+        <v>4.0387</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1915</v>
+        <v>4.0387</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1915</v>
+        <v>4.0387</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>230</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1915</v>
+        <v>4.0387</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8516</v>
+        <v>3.7276</v>
       </c>
       <c r="C7" t="n">
-        <v>1.91</v>
+        <v>1.8485</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1291</v>
+        <v>1.0923</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8516</v>
+        <v>3.7276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8442</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0073</v>
+        <v>2.9519</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8442</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8883</v>
+        <v>0.8177</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0073</v>
+        <v>2.9519</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -759,7 +759,7 @@
         <v>206</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8956</v>
+        <v>3.7696</v>
       </c>
       <c r="N7" t="n">
         <v>271</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2297</v>
+        <v>3.1706</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6016</v>
+        <v>1.5723</v>
       </c>
       <c r="D8" t="n">
-        <v>0.846</v>
+        <v>0.8386</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2297</v>
+        <v>3.1706</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0948</v>
+        <v>-0.0844</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3245</v>
+        <v>3.255</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0948</v>
+        <v>-0.0844</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0997</v>
+        <v>-0.089</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3245</v>
+        <v>3.255</v>
       </c>
       <c r="K8" t="n">
         <v>65</v>
@@ -805,7 +805,7 @@
         <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2248</v>
+        <v>3.166</v>
       </c>
       <c r="N8" t="n">
         <v>271</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1015</v>
+        <v>3.0179</v>
       </c>
       <c r="C9" t="n">
-        <v>1.538</v>
+        <v>1.4965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7877</v>
+        <v>0.769</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1015</v>
+        <v>3.0179</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2214</v>
+        <v>1.1552</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>1.8627</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2214</v>
+        <v>1.1552</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2852</v>
+        <v>1.2178</v>
       </c>
       <c r="J9" t="n">
-        <v>1.88</v>
+        <v>1.8627</v>
       </c>
       <c r="K9" t="n">
         <v>65</v>
@@ -851,7 +851,7 @@
         <v>206</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1652</v>
+        <v>3.0805</v>
       </c>
       <c r="N9" t="n">
         <v>271</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0463</v>
+        <v>2.9066</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5106</v>
+        <v>1.4413</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7625</v>
+        <v>0.7183</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0463</v>
+        <v>2.9066</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8561</v>
+        <v>0.7985</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1902</v>
+        <v>2.1081</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8561</v>
+        <v>0.7985</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9008</v>
+        <v>0.8417</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1902</v>
+        <v>2.1081</v>
       </c>
       <c r="K10" t="n">
         <v>65</v>
@@ -897,7 +897,7 @@
         <v>206</v>
       </c>
       <c r="M10" t="n">
-        <v>3.091</v>
+        <v>2.9498</v>
       </c>
       <c r="N10" t="n">
         <v>271</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8229</v>
+        <v>2.7455</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3998</v>
+        <v>1.3615</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6449</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8229</v>
+        <v>2.7455</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0562</v>
+        <v>-0.0479</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8791</v>
+        <v>2.7934</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0562</v>
+        <v>-0.0479</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0562</v>
+        <v>-0.0479</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8791</v>
+        <v>2.7934</v>
       </c>
       <c r="K11" t="n">
         <v>53</v>
@@ -943,7 +943,7 @@
         <v>204</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8229</v>
+        <v>2.7455</v>
       </c>
       <c r="N11" t="n">
         <v>257</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5535</v>
+        <v>2.5779</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2662</v>
+        <v>1.2783</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5382</v>
+        <v>0.5686</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5535</v>
+        <v>2.5779</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3568</v>
+        <v>2.3537</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1967</v>
+        <v>0.2242</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4335</v>
+        <v>2.4438</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5605</v>
+        <v>2.5761</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1967</v>
+        <v>0.2242</v>
       </c>
       <c r="K12" t="n">
         <v>89</v>
@@ -989,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7572</v>
+        <v>2.8003</v>
       </c>
       <c r="N12" t="n">
         <v>185</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7837</v>
+        <v>1.8146</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8845</v>
+        <v>0.8998</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1878</v>
+        <v>0.2208</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7837</v>
+        <v>1.8146</v>
       </c>
       <c r="F13" t="n">
-        <v>0.717</v>
+        <v>-0.6279</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0667</v>
+        <v>2.4425</v>
       </c>
       <c r="H13" t="n">
-        <v>0.717</v>
+        <v>-0.6279</v>
       </c>
       <c r="I13" t="n">
-        <v>0.717</v>
+        <v>-0.6279</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0667</v>
+        <v>2.4425</v>
       </c>
       <c r="K13" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="L13" t="n">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7837</v>
+        <v>1.8146</v>
       </c>
       <c r="N13" t="n">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7613</v>
+        <v>1.657</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8734</v>
+        <v>0.8217</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1776</v>
+        <v>0.1491</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7613</v>
+        <v>1.657</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6583</v>
+        <v>0.6109</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4196</v>
+        <v>1.0461</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6583</v>
+        <v>0.6109</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6583</v>
+        <v>0.6109</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4196</v>
+        <v>1.0461</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7613</v>
+        <v>1.657</v>
       </c>
       <c r="N14" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2074</v>
+        <v>1.159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5987</v>
+        <v>0.5747</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0746</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2074</v>
+        <v>1.159</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6172</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8246</v>
+        <v>1.7502</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6172</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6172</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8246</v>
+        <v>1.7502</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -1127,7 +1127,7 @@
         <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2074</v>
+        <v>1.159</v>
       </c>
       <c r="N15" t="n">
         <v>211</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9235</v>
+        <v>0.8879</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4579</v>
+        <v>0.4403</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2038</v>
+        <v>-0.2013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9235</v>
+        <v>0.8879</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7464</v>
+        <v>-0.7594</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6699</v>
+        <v>1.6473</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7464</v>
+        <v>-0.7594</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7464</v>
+        <v>-0.7594</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6699</v>
+        <v>1.6473</v>
       </c>
       <c r="K16" t="n">
         <v>114</v>
@@ -1173,7 +1173,7 @@
         <v>97</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9235</v>
+        <v>0.8879</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8264</v>
+        <v>0.8312</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4098</v>
+        <v>0.4122</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.248</v>
+        <v>-0.2271</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8264</v>
+        <v>0.8312</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8324</v>
+        <v>-0.4404</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.006</v>
+        <v>1.2716</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8324</v>
+        <v>-0.4404</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8759</v>
+        <v>-0.4404</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.006</v>
+        <v>1.2716</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8699</v>
+        <v>0.8312</v>
       </c>
       <c r="N17" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8076</v>
+        <v>0.8131</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4005</v>
+        <v>0.4032</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2566</v>
+        <v>-0.2354</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8076</v>
+        <v>0.8131</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4801</v>
+        <v>0.6379</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2877</v>
+        <v>0.1752</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4801</v>
+        <v>0.6379</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4801</v>
+        <v>0.7473</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2877</v>
+        <v>0.1752</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="L18" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8076000000000001</v>
+        <v>0.9225</v>
       </c>
       <c r="N18" t="n">
-        <v>257</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7188</v>
+        <v>0.7661</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3564</v>
+        <v>0.3799</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.297</v>
+        <v>-0.2568</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7188</v>
+        <v>0.7661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6054</v>
+        <v>0.7679</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1134</v>
+        <v>-0.0018</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6054</v>
+        <v>0.7679</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7052</v>
+        <v>0.8095</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1134</v>
+        <v>-0.0018</v>
       </c>
       <c r="K19" t="n">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="L19" t="n">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8186</v>
+        <v>0.8077</v>
       </c>
       <c r="N19" t="n">
-        <v>398</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6143</v>
+        <v>0.5445</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3046</v>
+        <v>0.27</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3446</v>
+        <v>-0.3577</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6143</v>
+        <v>0.5445</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1511</v>
+        <v>-0.1541</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7654</v>
+        <v>0.6985</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1511</v>
+        <v>-0.1541</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.155</v>
+        <v>-0.1582</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7654</v>
+        <v>0.6985</v>
       </c>
       <c r="K20" t="n">
         <v>89</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6103999999999999</v>
+        <v>0.5403</v>
       </c>
       <c r="N20" t="n">
         <v>173</v>
@@ -1366,265 +1366,265 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4774</v>
+        <v>0.4424</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2367</v>
+        <v>0.2194</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4069</v>
+        <v>-0.4043</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4774</v>
+        <v>0.4424</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1268</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6042</v>
+        <v>0.4424</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1268</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1268</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6042</v>
+        <v>0.4424</v>
       </c>
       <c r="K21" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4773999999999999</v>
+        <v>0.4424</v>
       </c>
       <c r="N21" t="n">
-        <v>257</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4593</v>
+        <v>0.3959</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2278</v>
+        <v>0.1963</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4151</v>
+        <v>-0.4254</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4593</v>
+        <v>0.3959</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4593</v>
+        <v>-0.046</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4593</v>
+        <v>-0.046</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="L22" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4593</v>
+        <v>0.4716</v>
       </c>
       <c r="N22" t="n">
-        <v>230</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4455</v>
+        <v>0.3383</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2209</v>
+        <v>0.1678</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4214</v>
+        <v>-0.4517</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4455</v>
+        <v>0.3383</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4286</v>
+        <v>0.3737</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0169</v>
+        <v>-0.0354</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4286</v>
+        <v>0.3737</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4993</v>
+        <v>0.3837</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0169</v>
+        <v>-0.0354</v>
       </c>
       <c r="K23" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="L23" t="n">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5162</v>
+        <v>0.3483</v>
       </c>
       <c r="N23" t="n">
-        <v>398</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4193</v>
+        <v>0.302</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2079</v>
+        <v>0.1498</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4333</v>
+        <v>-0.4682</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4193</v>
+        <v>0.302</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4179</v>
+        <v>-0.1634</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0014</v>
+        <v>0.4654</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4179</v>
+        <v>-0.1634</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4287</v>
+        <v>-0.1634</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0014</v>
+        <v>0.4654</v>
       </c>
       <c r="K24" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L24" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4301</v>
+        <v>0.302</v>
       </c>
       <c r="N24" t="n">
-        <v>173</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1549</v>
+        <v>0.1254</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0622</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5537</v>
+        <v>-0.5487</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1549</v>
+        <v>0.1254</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2278</v>
+        <v>0.1163</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3827</v>
+        <v>0.0091</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2278</v>
+        <v>0.1163</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2337</v>
+        <v>0.1226</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3827</v>
+        <v>0.0091</v>
       </c>
       <c r="K25" t="n">
         <v>89</v>
       </c>
       <c r="L25" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="M25" t="n">
-        <v>0.149</v>
+        <v>0.1317</v>
       </c>
       <c r="N25" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1208</v>
+        <v>0.0497</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0599</v>
+        <v>0.0246</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5692</v>
+        <v>-0.5831</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1208</v>
+        <v>0.0497</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0799</v>
+        <v>-0.2526</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0409</v>
+        <v>0.3023</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0799</v>
+        <v>-0.2526</v>
       </c>
       <c r="I26" t="n">
-        <v>0.082</v>
+        <v>-0.2593</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0409</v>
+        <v>0.3023</v>
       </c>
       <c r="K26" t="n">
         <v>89</v>
@@ -1633,7 +1633,7 @@
         <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1229</v>
+        <v>0.04300000000000004</v>
       </c>
       <c r="N26" t="n">
         <v>173</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1017</v>
+        <v>-0.0058</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0504</v>
+        <v>-0.0029</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5779</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1017</v>
+        <v>-0.0058</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0235</v>
+        <v>-0.0128</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0235</v>
+        <v>-0.0128</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0241</v>
+        <v>-0.0131</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="K27" t="n">
         <v>89</v>
@@ -1679,7 +1679,7 @@
         <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1023</v>
+        <v>-0.0061</v>
       </c>
       <c r="N27" t="n">
         <v>173</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0594</v>
+        <v>-0.0321</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0295</v>
+        <v>-0.0159</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5972</v>
+        <v>-0.6204</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0594</v>
+        <v>-0.0321</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0684</v>
+        <v>-0.0231</v>
       </c>
       <c r="G28" t="n">
         <v>-0.008999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0684</v>
+        <v>-0.0231</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0237</v>
       </c>
       <c r="J28" t="n">
         <v>-0.008999999999999999</v>
@@ -1722,47 +1722,47 @@
         <v>89</v>
       </c>
       <c r="L28" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>0.063</v>
+        <v>-0.0327</v>
       </c>
       <c r="N28" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1527</v>
+        <v>-0.1549</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0757</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6937</v>
+        <v>-0.6764</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1527</v>
+        <v>-0.1549</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2401</v>
+        <v>0.0359</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3928</v>
+        <v>-0.1908</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2401</v>
+        <v>0.0359</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2401</v>
+        <v>0.0359</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3928</v>
+        <v>-0.1908</v>
       </c>
       <c r="K29" t="n">
         <v>56</v>
@@ -1771,7 +1771,7 @@
         <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1527</v>
+        <v>-0.1549</v>
       </c>
       <c r="N29" t="n">
         <v>109</v>
@@ -1780,35 +1780,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.154</v>
+        <v>-0.1579</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0764</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6943</v>
+        <v>-0.6777</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.154</v>
+        <v>-0.1579</v>
       </c>
       <c r="F30" t="n">
-        <v>0.067</v>
+        <v>0.2016</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.221</v>
+        <v>-0.3595</v>
       </c>
       <c r="H30" t="n">
-        <v>0.067</v>
+        <v>0.2016</v>
       </c>
       <c r="I30" t="n">
-        <v>0.067</v>
+        <v>0.2016</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.221</v>
+        <v>-0.3595</v>
       </c>
       <c r="K30" t="n">
         <v>56</v>
@@ -1817,7 +1817,7 @@
         <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.154</v>
+        <v>-0.1579</v>
       </c>
       <c r="N30" t="n">
         <v>109</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2832</v>
+        <v>-0.3258</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1404</v>
+        <v>-0.1616</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7531</v>
+        <v>-0.7542</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2832</v>
+        <v>-0.3258</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2464</v>
+        <v>0.2127</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5296</v>
+        <v>-0.5385</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2464</v>
+        <v>0.2127</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2593</v>
+        <v>0.2242</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5296</v>
+        <v>-0.5385</v>
       </c>
       <c r="K31" t="n">
         <v>89</v>
@@ -1863,7 +1863,7 @@
         <v>96</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2703</v>
+        <v>-0.3143</v>
       </c>
       <c r="N31" t="n">
         <v>185</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3803</v>
+        <v>-0.368</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1886</v>
+        <v>-0.1825</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7973</v>
+        <v>-0.7734</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3803</v>
+        <v>-0.368</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3803</v>
+        <v>-0.368</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3803</v>
+        <v>-0.368</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>230</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3803</v>
+        <v>-0.368</v>
       </c>
       <c r="N32" t="n">
         <v>230</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4385</v>
+        <v>-0.4334</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2174</v>
+        <v>-0.2149</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8238</v>
+        <v>-0.8032</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4385</v>
+        <v>-0.4334</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0134</v>
+        <v>0.9942</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.4519</v>
+        <v>-1.4276</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0134</v>
+        <v>0.9942</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0663</v>
+        <v>1.048</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.4519</v>
+        <v>-1.4276</v>
       </c>
       <c r="K33" t="n">
         <v>89</v>
@@ -1955,7 +1955,7 @@
         <v>96</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3855999999999999</v>
+        <v>-0.3795999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>185</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7905</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.392</v>
+        <v>-0.4022</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9841</v>
+        <v>-0.9752</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7905</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7285</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.036</v>
+        <v>-0.0825</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7285</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7285</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.036</v>
+        <v>-0.0825</v>
       </c>
       <c r="K34" t="n">
         <v>56</v>
@@ -2001,7 +2001,7 @@
         <v>53</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7905</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>109</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4581</v>
+        <v>-0.4301</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0448</v>
+        <v>-1.0009</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6283</v>
+        <v>-0.5994</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2956</v>
+        <v>-0.2679</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6283</v>
+        <v>-0.5994</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6283</v>
+        <v>-0.5994</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2956</v>
+        <v>-0.2679</v>
       </c>
       <c r="K35" t="n">
         <v>56</v>
@@ -2047,7 +2047,7 @@
         <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9238999999999999</v>
+        <v>-0.8673000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>109</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2807</v>
+        <v>-1.3439</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6351</v>
+        <v>-0.6664</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2072</v>
+        <v>-1.218</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2807</v>
+        <v>-1.3439</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.334</v>
+        <v>-0.3578</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9467</v>
+        <v>-0.9861</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.334</v>
+        <v>-0.3578</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.334</v>
+        <v>-0.3578</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9467</v>
+        <v>-0.9861</v>
       </c>
       <c r="K36" t="n">
         <v>53</v>
@@ -2093,7 +2093,7 @@
         <v>204</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2807</v>
+        <v>-1.3439</v>
       </c>
       <c r="N36" t="n">
         <v>257</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4912</v>
+        <v>-1.4418</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7395</v>
+        <v>-0.715</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.303</v>
+        <v>-1.2626</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4912</v>
+        <v>-1.4418</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7126</v>
+        <v>-0.6875</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7786</v>
+        <v>-0.7543</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7126</v>
+        <v>-0.6875</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7126</v>
+        <v>-0.6875</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7786</v>
+        <v>-0.7543</v>
       </c>
       <c r="K37" t="n">
         <v>56</v>
@@ -2139,7 +2139,7 @@
         <v>53</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4912</v>
+        <v>-1.4418</v>
       </c>
       <c r="N37" t="n">
         <v>109</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6293</v>
+        <v>-1.5839</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8079</v>
+        <v>-0.7854</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3659</v>
+        <v>-1.3273</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6293</v>
+        <v>-1.5839</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.6293</v>
+        <v>-1.5839</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.6293</v>
+        <v>-1.5839</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6293</v>
+        <v>-1.5839</v>
       </c>
       <c r="N38" t="n">
         <v>230</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6512</v>
+        <v>-1.589</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8188</v>
+        <v>-0.788</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3759</v>
+        <v>-1.3297</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6512</v>
+        <v>-1.589</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0613</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.5604</v>
+        <v>-1.5277</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0613</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0955</v>
+        <v>-0.0646</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5604</v>
+        <v>-1.5277</v>
       </c>
       <c r="K39" t="n">
         <v>89</v>
@@ -2231,7 +2231,7 @@
         <v>96</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6559</v>
+        <v>-1.5923</v>
       </c>
       <c r="N39" t="n">
         <v>185</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2006</v>
+        <v>-2.1494</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0912</v>
+        <v>-1.0659</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.626</v>
+        <v>-1.5849</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2006</v>
+        <v>-2.1494</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5655</v>
+        <v>-1.5426</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6351</v>
+        <v>-0.6068</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5655</v>
+        <v>-1.5426</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5655</v>
+        <v>-1.5426</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6351</v>
+        <v>-0.6068</v>
       </c>
       <c r="K40" t="n">
         <v>114</v>
@@ -2277,7 +2277,7 @@
         <v>97</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.2006</v>
+        <v>-2.1494</v>
       </c>
       <c r="N40" t="n">
         <v>211</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4298</v>
+        <v>-2.4369</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2049</v>
+        <v>-1.2084</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7303</v>
+        <v>-1.7159</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4298</v>
+        <v>-2.4369</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.4298</v>
+        <v>-2.4369</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.4298</v>
+        <v>-2.4369</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>230</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4298</v>
+        <v>-2.4369</v>
       </c>
       <c r="N41" t="n">
         <v>230</v>
@@ -2429,10 +2429,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="J2" t="n">
-        <v>17.8416</v>
+        <v>15.9057</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2769</v>
+        <v>0.2261</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4763</v>
+        <v>6.1047</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.24</v>
+        <v>0.1938</v>
       </c>
       <c r="J4" t="n">
-        <v>6.48</v>
+        <v>5.2326</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2272</v>
+        <v>0.1826</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1344</v>
+        <v>4.9302</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2157</v>
+        <v>-0.196</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.8239</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4889</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>13.2003</v>
+        <v>13.6782</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0267</v>
+        <v>-0.0195</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7209</v>
+        <v>-0.5265</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2753</v>
+        <v>-0.2571</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.4331</v>
+        <v>-6.9417</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3223</v>
+        <v>-0.3056</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.7021</v>
+        <v>-8.251200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.552</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.904</v>
+        <v>-15.093</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0052</v>
+        <v>-0.0007</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1404</v>
+        <v>-0.0189</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0235</v>
+        <v>-0.0162</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6345</v>
+        <v>-0.4374</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2448</v>
+        <v>-0.2268</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.6096</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2639</v>
+        <v>-0.2459</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.1253</v>
+        <v>-6.6393</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4638</v>
+        <v>-0.4586</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.5226</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.74</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5397</v>
+        <v>1.5709</v>
       </c>
       <c r="J17" t="n">
-        <v>41.5719</v>
+        <v>42.4143</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.51</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1431</v>
+        <v>1.1513</v>
       </c>
       <c r="J18" t="n">
-        <v>30.8637</v>
+        <v>31.0851</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2749</v>
+        <v>0.2438</v>
       </c>
       <c r="J19" t="n">
-        <v>7.4223</v>
+        <v>6.5826</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1442</v>
+        <v>-0.1176</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.8934</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2466</v>
+        <v>-0.2109</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.6582</v>
+        <v>-5.6943</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2015</v>
+        <v>-0.1858</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.433</v>
+        <v>-4.0876</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.321</v>
+        <v>-0.3094</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.062</v>
+        <v>-6.8068</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3478</v>
+        <v>-0.3367</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.6516</v>
+        <v>-7.4074</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.55</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.5898</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.53</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4607</v>
+        <v>-0.4549</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.1354</v>
+        <v>-10.0078</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7316</v>
+        <v>1.7666</v>
       </c>
       <c r="J27" t="n">
-        <v>38.0952</v>
+        <v>38.8652</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.48</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0575</v>
+        <v>1.0623</v>
       </c>
       <c r="J28" t="n">
-        <v>23.265</v>
+        <v>23.3706</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.41</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9335</v>
+        <v>0.9283</v>
       </c>
       <c r="J29" t="n">
-        <v>20.537</v>
+        <v>20.4226</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4005</v>
+        <v>0.3688</v>
       </c>
       <c r="J30" t="n">
-        <v>8.811</v>
+        <v>8.1136</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.12</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3272</v>
+        <v>0.2947</v>
       </c>
       <c r="J31" t="n">
-        <v>7.1984</v>
+        <v>6.4834</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1169</v>
+        <v>0.0871</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2732</v>
+        <v>2.4388</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0895</v>
+        <v>0.0646</v>
       </c>
       <c r="J33" t="n">
-        <v>2.506</v>
+        <v>1.8088</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1395</v>
+        <v>-0.1219</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.906</v>
+        <v>-3.4132</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1528</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.8132</v>
+        <v>-4.2784</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3386</v>
+        <v>-0.3227</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.4808</v>
+        <v>-9.035600000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9448</v>
+        <v>0.9332</v>
       </c>
       <c r="J37" t="n">
-        <v>26.4544</v>
+        <v>26.1296</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6684</v>
+        <v>0.6383</v>
       </c>
       <c r="J38" t="n">
-        <v>18.7152</v>
+        <v>17.8724</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6271</v>
+        <v>0.5957</v>
       </c>
       <c r="J39" t="n">
-        <v>17.5588</v>
+        <v>16.6796</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.24</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6271</v>
+        <v>0.5957</v>
       </c>
       <c r="J40" t="n">
-        <v>17.5588</v>
+        <v>16.6796</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2404</v>
+        <v>-0.2041</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.7312</v>
+        <v>-5.7148</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1877</v>
+        <v>-0.1696</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.9417</v>
+        <v>-3.5616</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.312</v>
+        <v>-0.3013</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.552</v>
+        <v>-6.3273</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.6</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3937</v>
+        <v>-0.3858</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.2677</v>
+        <v>-8.101800000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4795</v>
+        <v>-0.4759</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.0695</v>
+        <v>-9.9939</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5854</v>
+        <v>-0.5944</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.2934</v>
+        <v>-12.4824</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.73</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3547</v>
+        <v>1.3777</v>
       </c>
       <c r="J47" t="n">
-        <v>28.4487</v>
+        <v>28.9317</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0655</v>
+        <v>1.0794</v>
       </c>
       <c r="J48" t="n">
-        <v>22.3755</v>
+        <v>22.6674</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.49</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0521</v>
+        <v>1.0647</v>
       </c>
       <c r="J49" t="n">
-        <v>22.0941</v>
+        <v>22.3587</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.48</v>
       </c>
       <c r="I50" t="n">
-        <v>1.0384</v>
+        <v>1.0495</v>
       </c>
       <c r="J50" t="n">
-        <v>21.8064</v>
+        <v>22.0395</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2162</v>
+        <v>0.184</v>
       </c>
       <c r="J51" t="n">
-        <v>4.5402</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9366</v>
+        <v>0.9232</v>
       </c>
       <c r="J52" t="n">
-        <v>24.3516</v>
+        <v>24.0032</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5911</v>
+        <v>0.5564</v>
       </c>
       <c r="J53" t="n">
-        <v>15.3686</v>
+        <v>14.4664</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4824</v>
+        <v>0.4464</v>
       </c>
       <c r="J54" t="n">
-        <v>12.5424</v>
+        <v>11.6064</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3651</v>
+        <v>0.3303</v>
       </c>
       <c r="J55" t="n">
-        <v>9.492599999999999</v>
+        <v>8.5878</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1669</v>
+        <v>-0.1354</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.3394</v>
+        <v>-3.5204</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.22</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4868</v>
+        <v>0.4296</v>
       </c>
       <c r="J57" t="n">
-        <v>12.6568</v>
+        <v>11.1696</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2673</v>
+        <v>0.2192</v>
       </c>
       <c r="J58" t="n">
-        <v>6.9498</v>
+        <v>5.6992</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0683</v>
+        <v>-0.0559</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.7758</v>
+        <v>-1.4534</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.79</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2557</v>
+        <v>-0.236</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.6482</v>
+        <v>-6.136</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4487</v>
+        <v>-0.4429</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.6662</v>
+        <v>-11.5154</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.92</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6527</v>
+        <v>1.7053</v>
       </c>
       <c r="J62" t="n">
-        <v>44.6229</v>
+        <v>46.0431</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8734</v>
+        <v>0.8541</v>
       </c>
       <c r="J63" t="n">
-        <v>23.5818</v>
+        <v>23.0607</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3109</v>
+        <v>0.278</v>
       </c>
       <c r="J64" t="n">
-        <v>8.394299999999999</v>
+        <v>7.506</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.482</v>
+        <v>-0.4419</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.014</v>
+        <v>-11.9313</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-20.4822</v>
+        <v>-19.8288</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2302</v>
+        <v>0.1856</v>
       </c>
       <c r="J67" t="n">
-        <v>6.2154</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1147</v>
+        <v>0.0851</v>
       </c>
       <c r="J68" t="n">
-        <v>3.0969</v>
+        <v>2.2977</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0121</v>
+        <v>0.008</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3267</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2244</v>
+        <v>-0.2044</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.0588</v>
+        <v>-5.5188</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3941</v>
+        <v>-0.3826</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.6407</v>
+        <v>-10.3302</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7096</v>
+        <v>0.681</v>
       </c>
       <c r="J72" t="n">
-        <v>20.5784</v>
+        <v>19.749</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6274</v>
+        <v>0.5959</v>
       </c>
       <c r="J73" t="n">
-        <v>18.1946</v>
+        <v>17.2811</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6274</v>
+        <v>0.5959</v>
       </c>
       <c r="J74" t="n">
-        <v>18.1946</v>
+        <v>17.2811</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5859</v>
+        <v>0.5533</v>
       </c>
       <c r="J75" t="n">
-        <v>16.9911</v>
+        <v>16.0457</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3076</v>
+        <v>0.2752</v>
       </c>
       <c r="J76" t="n">
-        <v>8.920400000000001</v>
+        <v>7.9808</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.55</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0176</v>
+        <v>1.0061</v>
       </c>
       <c r="J77" t="n">
-        <v>29.5104</v>
+        <v>29.1769</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.8</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.9832</v>
+        <v>-6.4206</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.9832</v>
+        <v>-6.4206</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2604</v>
+        <v>-0.2412</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.5516</v>
+        <v>-6.9948</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.46</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5472</v>
+        <v>-0.554</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.8688</v>
+        <v>-16.066</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6219</v>
       </c>
       <c r="J82" t="n">
-        <v>23.6808</v>
+        <v>22.3884</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3024</v>
+        <v>0.2644</v>
       </c>
       <c r="J83" t="n">
-        <v>10.8864</v>
+        <v>9.5184</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2485</v>
+        <v>0.2136</v>
       </c>
       <c r="J84" t="n">
-        <v>8.946</v>
+        <v>7.6896</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1912</v>
+        <v>0.1607</v>
       </c>
       <c r="J85" t="n">
-        <v>6.8832</v>
+        <v>5.7852</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4073</v>
+        <v>-0.3642</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.6628</v>
+        <v>-13.1112</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.24</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5043</v>
+        <v>0.4455</v>
       </c>
       <c r="J87" t="n">
-        <v>18.1548</v>
+        <v>16.038</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3125</v>
+        <v>0.2609</v>
       </c>
       <c r="J88" t="n">
-        <v>11.25</v>
+        <v>9.3924</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0751</v>
+        <v>0.0534</v>
       </c>
       <c r="J89" t="n">
-        <v>2.7036</v>
+        <v>1.9224</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.261</v>
+        <v>-0.2414</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.396000000000001</v>
+        <v>-8.6904</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2997</v>
+        <v>-0.2817</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7892</v>
+        <v>-10.1412</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4295</v>
+        <v>0.3801</v>
       </c>
       <c r="J92" t="n">
-        <v>10.7375</v>
+        <v>9.5025</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.785</v>
+        <v>-1.4875</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1879</v>
+        <v>-0.1703</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.6975</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.256</v>
+        <v>-0.2376</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5772</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.43</v>
+        <v>-14.705</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7153</v>
+        <v>0.701</v>
       </c>
       <c r="J97" t="n">
-        <v>17.8825</v>
+        <v>17.525</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.23</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5641</v>
+        <v>0.5563</v>
       </c>
       <c r="J98" t="n">
-        <v>14.1025</v>
+        <v>13.9075</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.22</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5485</v>
+        <v>0.5413</v>
       </c>
       <c r="J99" t="n">
-        <v>13.7125</v>
+        <v>13.5325</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4852</v>
+        <v>0.4672</v>
       </c>
       <c r="J100" t="n">
-        <v>12.13</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1691</v>
+        <v>0.143</v>
       </c>
       <c r="J101" t="n">
-        <v>4.2275</v>
+        <v>3.575</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.5735</v>
       </c>
       <c r="J102" t="n">
-        <v>17.4</v>
+        <v>16.6315</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5649</v>
+        <v>0.5399</v>
       </c>
       <c r="J103" t="n">
-        <v>16.3821</v>
+        <v>15.6571</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2388</v>
+        <v>-0.2186</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.9252</v>
+        <v>-6.3394</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.344</v>
+        <v>-0.3287</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.976000000000001</v>
+        <v>-9.532299999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3805</v>
+        <v>-0.3681</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.0345</v>
+        <v>-10.6749</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6867</v>
+        <v>0.6716</v>
       </c>
       <c r="J107" t="n">
-        <v>19.9143</v>
+        <v>19.4764</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.42</v>
+        <v>0.3819</v>
       </c>
       <c r="J108" t="n">
-        <v>12.18</v>
+        <v>11.0751</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3236</v>
+        <v>0.287</v>
       </c>
       <c r="J109" t="n">
-        <v>9.384399999999999</v>
+        <v>8.323</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0426</v>
+        <v>0.0317</v>
       </c>
       <c r="J110" t="n">
-        <v>1.2354</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.2272</v>
+        <v>-1.6385</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5649</v>
+        <v>0.5543</v>
       </c>
       <c r="J112" t="n">
-        <v>16.947</v>
+        <v>16.629</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4119</v>
+        <v>0.3695</v>
       </c>
       <c r="J113" t="n">
-        <v>12.357</v>
+        <v>11.085</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1488</v>
+        <v>0.118</v>
       </c>
       <c r="J114" t="n">
-        <v>4.464</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5739</v>
+        <v>-0.5343</v>
       </c>
       <c r="J115" t="n">
-        <v>-17.217</v>
+        <v>-16.029</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.1265</v>
+        <v>-1.1378</v>
       </c>
       <c r="J116" t="n">
-        <v>-33.795</v>
+        <v>-34.134</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.04</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2759</v>
+        <v>1.2514</v>
       </c>
       <c r="J117" t="n">
-        <v>38.277</v>
+        <v>37.542</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1357</v>
+        <v>0.1068</v>
       </c>
       <c r="J118" t="n">
-        <v>4.071</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0609</v>
+        <v>0.0447</v>
       </c>
       <c r="J119" t="n">
-        <v>1.827</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2819</v>
+        <v>-0.264</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.457000000000001</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3662</v>
+        <v>-0.3542</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.986</v>
+        <v>-10.626</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4997</v>
+        <v>0.5262</v>
       </c>
       <c r="J122" t="n">
-        <v>20.4877</v>
+        <v>21.5742</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.347</v>
+        <v>0.3386</v>
       </c>
       <c r="J123" t="n">
-        <v>14.227</v>
+        <v>13.8826</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1297</v>
+        <v>0.1143</v>
       </c>
       <c r="J124" t="n">
-        <v>5.3177</v>
+        <v>4.6863</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1939</v>
+        <v>-0.1733</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.9499</v>
+        <v>-7.1053</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3598</v>
+        <v>-0.3462</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.7518</v>
+        <v>-14.1942</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2633</v>
+        <v>0.2116</v>
       </c>
       <c r="J127" t="n">
-        <v>10.7953</v>
+        <v>8.675599999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1817</v>
+        <v>0.1406</v>
       </c>
       <c r="J128" t="n">
-        <v>7.4497</v>
+        <v>5.7646</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1374</v>
+        <v>0.1035</v>
       </c>
       <c r="J129" t="n">
-        <v>5.6334</v>
+        <v>4.2435</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1058</v>
+        <v>0.0779</v>
       </c>
       <c r="J130" t="n">
-        <v>4.3378</v>
+        <v>3.1939</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1846</v>
+        <v>-0.164</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.5686</v>
+        <v>-6.724</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.21</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7686</v>
+        <v>1.8149</v>
       </c>
       <c r="J132" t="n">
-        <v>35.372</v>
+        <v>36.298</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.86</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3625</v>
+        <v>1.3691</v>
       </c>
       <c r="J133" t="n">
-        <v>27.25</v>
+        <v>27.382</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6153</v>
+        <v>0.6118</v>
       </c>
       <c r="J134" t="n">
-        <v>12.306</v>
+        <v>12.236</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4368</v>
+        <v>0.4087</v>
       </c>
       <c r="J135" t="n">
-        <v>8.736000000000001</v>
+        <v>8.173999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6178</v>
+        <v>-0.5916</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.356</v>
+        <v>-11.832</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.82</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1758</v>
+        <v>-0.1569</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.516</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.7</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3018</v>
+        <v>-0.2906</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.036</v>
+        <v>-5.812</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.59</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4015</v>
+        <v>-0.394</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.029999999999999</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4704</v>
+        <v>-0.4661</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.407999999999999</v>
+        <v>-9.321999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.35</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6116</v>
+        <v>-0.6248</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.232</v>
+        <v>-12.496</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4439</v>
+        <v>0.3931</v>
       </c>
       <c r="J142" t="n">
-        <v>11.5414</v>
+        <v>10.2206</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.078</v>
+        <v>-0.0653</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.028</v>
+        <v>-1.6978</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.87</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1707</v>
+        <v>-0.152</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.4382</v>
+        <v>-3.952</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3091</v>
+        <v>-0.2914</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.0366</v>
+        <v>-7.5764</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.762</v>
+        <v>-8.343400000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8119</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>21.1094</v>
+        <v>20.6934</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8119</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>21.1094</v>
+        <v>20.6934</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.489</v>
+        <v>0.4696</v>
       </c>
       <c r="J149" t="n">
-        <v>12.714</v>
+        <v>12.2096</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.04</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1461</v>
+        <v>0.1217</v>
       </c>
       <c r="J150" t="n">
-        <v>3.7986</v>
+        <v>3.1642</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7073</v>
+        <v>-0.6778</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.3898</v>
+        <v>-17.6228</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.13</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3362</v>
+        <v>0.2845</v>
       </c>
       <c r="J152" t="n">
-        <v>9.7498</v>
+        <v>8.250500000000001</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3169</v>
+        <v>0.2662</v>
       </c>
       <c r="J153" t="n">
-        <v>9.190099999999999</v>
+        <v>7.7198</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2021</v>
+        <v>-0.1825</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.8609</v>
+        <v>-5.2925</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.281</v>
+        <v>-0.2623</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.148999999999999</v>
+        <v>-7.6067</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4187</v>
+        <v>-0.4094</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.1423</v>
+        <v>-11.8726</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.708</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>20.532</v>
+        <v>20.097</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5694</v>
+        <v>0.5598</v>
       </c>
       <c r="J158" t="n">
-        <v>16.5126</v>
+        <v>16.2342</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4886</v>
+        <v>0.4693</v>
       </c>
       <c r="J159" t="n">
-        <v>14.1694</v>
+        <v>13.6097</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4362</v>
+        <v>0.4022</v>
       </c>
       <c r="J160" t="n">
-        <v>12.6498</v>
+        <v>11.6638</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3722</v>
+        <v>-0.3304</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.7938</v>
+        <v>-9.5816</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0197</v>
+        <v>0.0146</v>
       </c>
       <c r="J162" t="n">
-        <v>0.591</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0485</v>
+        <v>-0.0389</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.455</v>
+        <v>-1.167</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.138</v>
+        <v>-0.1212</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.14</v>
+        <v>-3.636</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.27</v>
+        <v>-0.2511</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.1</v>
+        <v>-7.533</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2891</v>
+        <v>-0.2708</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.673</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8752</v>
+        <v>0.8598</v>
       </c>
       <c r="J167" t="n">
-        <v>26.256</v>
+        <v>25.794</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4861</v>
+        <v>0.4677</v>
       </c>
       <c r="J168" t="n">
-        <v>14.583</v>
+        <v>14.031</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4695</v>
+        <v>0.4455</v>
       </c>
       <c r="J169" t="n">
-        <v>14.085</v>
+        <v>13.365</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3373</v>
+        <v>0.3036</v>
       </c>
       <c r="J170" t="n">
-        <v>10.119</v>
+        <v>9.108000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.201</v>
+        <v>0.1728</v>
       </c>
       <c r="J171" t="n">
-        <v>6.03</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3123</v>
+        <v>0.2557</v>
       </c>
       <c r="J172" t="n">
-        <v>9.056699999999999</v>
+        <v>7.4153</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2616</v>
+        <v>0.2102</v>
       </c>
       <c r="J173" t="n">
-        <v>7.5864</v>
+        <v>6.0958</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2353</v>
+        <v>0.1871</v>
       </c>
       <c r="J174" t="n">
-        <v>6.8237</v>
+        <v>5.4259</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0473</v>
+        <v>-0.0358</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.3717</v>
+        <v>-1.0382</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2175</v>
+        <v>-0.1971</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.3075</v>
+        <v>-5.7159</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4414</v>
+        <v>0.447</v>
       </c>
       <c r="J177" t="n">
-        <v>12.8006</v>
+        <v>12.963</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3699</v>
+        <v>0.3637</v>
       </c>
       <c r="J178" t="n">
-        <v>10.7271</v>
+        <v>10.5473</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1447</v>
+        <v>0.1294</v>
       </c>
       <c r="J179" t="n">
-        <v>4.1963</v>
+        <v>3.7526</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0746</v>
+        <v>0.063</v>
       </c>
       <c r="J180" t="n">
-        <v>2.1634</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.64</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4062</v>
+        <v>-0.3972</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.7798</v>
+        <v>-11.5188</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.74</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2219</v>
+        <v>-0.1983</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.9942</v>
+        <v>-3.5694</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.6</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3699</v>
+        <v>-0.3639</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.6582</v>
+        <v>-6.5502</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.45</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.5043</v>
+        <v>-0.5056</v>
       </c>
       <c r="J184" t="n">
-        <v>-9.077400000000001</v>
+        <v>-9.1008</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.32</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6208</v>
+        <v>-0.6341</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.1744</v>
+        <v>-11.4138</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6484</v>
+        <v>-0.6662</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.6712</v>
+        <v>-11.9916</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.5994</v>
+        <v>1.6256</v>
       </c>
       <c r="J187" t="n">
-        <v>28.7892</v>
+        <v>29.2608</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.88</v>
       </c>
       <c r="I188" t="n">
-        <v>1.3607</v>
+        <v>1.3692</v>
       </c>
       <c r="J188" t="n">
-        <v>24.4926</v>
+        <v>24.6456</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.6</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0313</v>
+        <v>1.0286</v>
       </c>
       <c r="J189" t="n">
-        <v>18.5634</v>
+        <v>18.5148</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.53</v>
       </c>
       <c r="I190" t="n">
-        <v>0.9442</v>
+        <v>0.9405</v>
       </c>
       <c r="J190" t="n">
-        <v>16.9956</v>
+        <v>16.929</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.06</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1358</v>
+        <v>0.101</v>
       </c>
       <c r="J191" t="n">
-        <v>2.4444</v>
+        <v>1.818</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.22</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5542</v>
+        <v>0.5123</v>
       </c>
       <c r="J192" t="n">
-        <v>13.3008</v>
+        <v>12.2952</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.0856</v>
+        <v>-1.7568</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3782</v>
+        <v>-0.3652</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.0768</v>
+        <v>-8.764799999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4317</v>
+        <v>-0.423</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.3608</v>
+        <v>-10.152</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5365</v>
+        <v>-0.5403</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.876</v>
+        <v>-12.9672</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0505</v>
+        <v>1.0567</v>
       </c>
       <c r="J197" t="n">
-        <v>25.212</v>
+        <v>25.3608</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0206</v>
+        <v>1.0221</v>
       </c>
       <c r="J198" t="n">
-        <v>24.4944</v>
+        <v>24.5304</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.26</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6637</v>
+        <v>0.6357</v>
       </c>
       <c r="J199" t="n">
-        <v>15.9288</v>
+        <v>15.2568</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3263</v>
+        <v>0.2941</v>
       </c>
       <c r="J200" t="n">
-        <v>7.8312</v>
+        <v>7.0584</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0159</v>
+        <v>0.0058</v>
       </c>
       <c r="J201" t="n">
-        <v>0.3816</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6347</v>
+        <v>0.5641</v>
       </c>
       <c r="J202" t="n">
-        <v>19.041</v>
+        <v>16.923</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2192</v>
+        <v>0.1736</v>
       </c>
       <c r="J203" t="n">
-        <v>6.576</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1643</v>
+        <v>0.127</v>
       </c>
       <c r="J204" t="n">
-        <v>4.929</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1661</v>
+        <v>-0.1458</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.983</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1989</v>
+        <v>-0.1784</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.967</v>
+        <v>-5.352</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5485</v>
+        <v>0.5674</v>
       </c>
       <c r="J207" t="n">
-        <v>16.455</v>
+        <v>17.022</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.97</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0565</v>
+        <v>-0.0448</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.695</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1775</v>
+        <v>-0.1573</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.325</v>
+        <v>-4.719</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.84</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2092</v>
+        <v>-0.1887</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.276</v>
+        <v>-5.661</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2397</v>
+        <v>-0.2195</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.191</v>
+        <v>-6.585</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3993</v>
+        <v>0.343</v>
       </c>
       <c r="J212" t="n">
-        <v>13.9755</v>
+        <v>12.005</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3641</v>
+        <v>0.3095</v>
       </c>
       <c r="J213" t="n">
-        <v>12.7435</v>
+        <v>10.8325</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0525</v>
       </c>
       <c r="J214" t="n">
-        <v>2.569</v>
+        <v>1.8375</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2324</v>
+        <v>-0.212</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.134</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.82</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2324</v>
+        <v>-0.212</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.134</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9797</v>
+        <v>0.9734</v>
       </c>
       <c r="J217" t="n">
-        <v>34.2895</v>
+        <v>34.069</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9615</v>
+        <v>0.952</v>
       </c>
       <c r="J218" t="n">
-        <v>33.6525</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.09</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2999</v>
+        <v>0.2632</v>
       </c>
       <c r="J219" t="n">
-        <v>10.4965</v>
+        <v>9.212</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5817</v>
+        <v>-0.543</v>
       </c>
       <c r="J220" t="n">
-        <v>-20.3595</v>
+        <v>-19.005</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7108</v>
       </c>
       <c r="J221" t="n">
-        <v>-25.879</v>
+        <v>-24.878</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.92</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6017</v>
+        <v>1.642</v>
       </c>
       <c r="J222" t="n">
-        <v>35.2374</v>
+        <v>36.124</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1143</v>
+        <v>1.1284</v>
       </c>
       <c r="J223" t="n">
-        <v>24.5146</v>
+        <v>24.8248</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.26</v>
       </c>
       <c r="I224" t="n">
-        <v>0.65</v>
+        <v>0.6263</v>
       </c>
       <c r="J224" t="n">
-        <v>14.3</v>
+        <v>13.7786</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5218</v>
+        <v>0.493</v>
       </c>
       <c r="J225" t="n">
-        <v>11.4796</v>
+        <v>10.846</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2653</v>
+        <v>-0.2325</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.8366</v>
+        <v>-5.115</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.88</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.141</v>
+        <v>-0.1255</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.102</v>
+        <v>-2.761</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1961</v>
+        <v>-0.1806</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.3142</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2566</v>
+        <v>-0.2414</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.6452</v>
+        <v>-5.3108</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3828</v>
+        <v>-0.3705</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.4216</v>
+        <v>-8.151</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.54</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4627</v>
+        <v>-0.4569</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.1794</v>
+        <v>-10.0518</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1422</v>
+        <v>1.155</v>
       </c>
       <c r="J232" t="n">
-        <v>38.8348</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7504</v>
+        <v>0.7237</v>
       </c>
       <c r="J233" t="n">
-        <v>25.5136</v>
+        <v>24.6058</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5224</v>
+        <v>0.4887</v>
       </c>
       <c r="J234" t="n">
-        <v>17.7616</v>
+        <v>16.6158</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5003</v>
+        <v>0.4664</v>
       </c>
       <c r="J235" t="n">
-        <v>17.0102</v>
+        <v>15.8576</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4601</v>
+        <v>-0.42</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.6434</v>
+        <v>-14.28</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3811</v>
+        <v>0.3285</v>
       </c>
       <c r="J237" t="n">
-        <v>12.9574</v>
+        <v>11.169</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2631</v>
+        <v>0.2168</v>
       </c>
       <c r="J238" t="n">
-        <v>8.945399999999999</v>
+        <v>7.3712</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2499</v>
+        <v>-0.2306</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.496600000000001</v>
+        <v>-7.8404</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.66</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3717</v>
+        <v>-0.358</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.6378</v>
+        <v>-12.172</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3717</v>
+        <v>-0.358</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.6378</v>
+        <v>-12.172</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.01</v>
       </c>
       <c r="I242" t="n">
-        <v>1.5592</v>
+        <v>1.584</v>
       </c>
       <c r="J242" t="n">
-        <v>31.184</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I243" t="n">
-        <v>1.4521</v>
+        <v>1.4663</v>
       </c>
       <c r="J243" t="n">
-        <v>29.042</v>
+        <v>29.326</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.09</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2545</v>
+        <v>0.2229</v>
       </c>
       <c r="J244" t="n">
-        <v>5.09</v>
+        <v>4.458</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2668</v>
+        <v>-0.2343</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.336</v>
+        <v>-4.686</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2972</v>
+        <v>-0.2633</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.944</v>
+        <v>-5.266</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0573</v>
+        <v>-0.0416</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.146</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2001</v>
+        <v>-0.1847</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.002</v>
+        <v>-3.694</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2313</v>
+        <v>-0.2166</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.626</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.64</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3693</v>
+        <v>-0.3571</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.386</v>
+        <v>-7.142</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.27</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6919</v>
+        <v>-0.722</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.838</v>
+        <v>-14.44</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.25</v>
       </c>
       <c r="I252" t="n">
-        <v>1.8175</v>
+        <v>1.8705</v>
       </c>
       <c r="J252" t="n">
-        <v>39.985</v>
+        <v>41.151</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8546</v>
+        <v>0.8458</v>
       </c>
       <c r="J253" t="n">
-        <v>18.8012</v>
+        <v>18.6076</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.719</v>
+        <v>0.7125</v>
       </c>
       <c r="J254" t="n">
-        <v>15.818</v>
+        <v>15.675</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6317</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>13.8974</v>
+        <v>13.805</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3366</v>
+        <v>-0.3041</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.4052</v>
+        <v>-6.6902</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0198</v>
+        <v>0.0419</v>
       </c>
       <c r="J257" t="n">
-        <v>0.4356</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.72</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2957</v>
+        <v>-0.2829</v>
       </c>
       <c r="J258" t="n">
-        <v>-6.5054</v>
+        <v>-6.2238</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.63</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3751</v>
+        <v>-0.3638</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.2522</v>
+        <v>-8.0036</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.62</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3838</v>
+        <v>-0.3729</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.4436</v>
+        <v>-8.203799999999999</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5945</v>
+        <v>-0.6058</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.079</v>
+        <v>-13.3276</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.36</v>
       </c>
       <c r="I262" t="n">
-        <v>0.5286</v>
+        <v>0.5618</v>
       </c>
       <c r="J262" t="n">
-        <v>14.2722</v>
+        <v>15.1686</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0531</v>
       </c>
       <c r="J263" t="n">
-        <v>1.7874</v>
+        <v>1.4337</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.86</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1845</v>
+        <v>-0.1646</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.9815</v>
+        <v>-4.4442</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.9559</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3502</v>
+        <v>-0.3351</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.455399999999999</v>
+        <v>-9.047700000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.308</v>
+        <v>0.2522</v>
       </c>
       <c r="J267" t="n">
-        <v>8.316000000000001</v>
+        <v>6.8094</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2956</v>
+        <v>0.2411</v>
       </c>
       <c r="J268" t="n">
-        <v>7.9812</v>
+        <v>6.5097</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.14</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2318</v>
+        <v>0.1848</v>
       </c>
       <c r="J269" t="n">
-        <v>6.2586</v>
+        <v>4.9896</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.06</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1188</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J270" t="n">
-        <v>3.2076</v>
+        <v>2.4138</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1553</v>
+        <v>-0.1352</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.1931</v>
+        <v>-3.6504</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8753</v>
+        <v>0.8608</v>
       </c>
       <c r="J272" t="n">
-        <v>23.6331</v>
+        <v>23.2416</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3534</v>
+        <v>0.3138</v>
       </c>
       <c r="J273" t="n">
-        <v>9.5418</v>
+        <v>8.4726</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1477</v>
+        <v>-0.1171</v>
       </c>
       <c r="J274" t="n">
-        <v>-3.9879</v>
+        <v>-3.1617</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2133</v>
+        <v>-0.1767</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.7591</v>
+        <v>-4.7709</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3559</v>
+        <v>-0.3132</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.609299999999999</v>
+        <v>-8.4564</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3801</v>
+        <v>0.3246</v>
       </c>
       <c r="J277" t="n">
-        <v>10.2627</v>
+        <v>8.764200000000001</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1236</v>
+        <v>0.0936</v>
       </c>
       <c r="J278" t="n">
-        <v>3.3372</v>
+        <v>2.5272</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0427</v>
+        <v>0.0291</v>
       </c>
       <c r="J279" t="n">
-        <v>1.1529</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0257</v>
+        <v>-0.0184</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.6939</v>
+        <v>-0.4968</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2229</v>
+        <v>-0.2024</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.0183</v>
+        <v>-5.4648</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1242</v>
+        <v>1.1193</v>
       </c>
       <c r="J282" t="n">
-        <v>33.726</v>
+        <v>33.579</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6525</v>
       </c>
       <c r="J283" t="n">
-        <v>20.004</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5729</v>
+        <v>0.5624</v>
       </c>
       <c r="J284" t="n">
-        <v>17.187</v>
+        <v>16.872</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6815</v>
+        <v>-0.6496</v>
       </c>
       <c r="J285" t="n">
-        <v>-20.445</v>
+        <v>-19.488</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7038</v>
+        <v>-0.6735</v>
       </c>
       <c r="J286" t="n">
-        <v>-21.114</v>
+        <v>-20.205</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.28</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5406</v>
+        <v>0.514</v>
       </c>
       <c r="J287" t="n">
-        <v>16.218</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1766</v>
+        <v>0.138</v>
       </c>
       <c r="J288" t="n">
-        <v>5.298</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1055</v>
+        <v>0.0776</v>
       </c>
       <c r="J289" t="n">
-        <v>3.165</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2974</v>
+        <v>-0.2792</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.922000000000001</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3534</v>
+        <v>-0.3388</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.602</v>
+        <v>-10.164</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9517</v>
+        <v>0.9379</v>
       </c>
       <c r="J292" t="n">
-        <v>25.6959</v>
+        <v>25.3233</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9238</v>
+        <v>0.9092</v>
       </c>
       <c r="J293" t="n">
-        <v>24.9426</v>
+        <v>24.5484</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1444</v>
+        <v>0.1202</v>
       </c>
       <c r="J294" t="n">
-        <v>3.8988</v>
+        <v>3.2454</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1647</v>
+        <v>-0.1332</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.4469</v>
+        <v>-3.5964</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5248</v>
+        <v>-0.4853</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.1696</v>
+        <v>-13.1031</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.17</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4141</v>
+        <v>0.3607</v>
       </c>
       <c r="J297" t="n">
-        <v>11.1807</v>
+        <v>9.738899999999999</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.96</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0634</v>
+        <v>-0.0522</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.7118</v>
+        <v>-1.4094</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.88</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1598</v>
+        <v>-0.1418</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.3146</v>
+        <v>-3.8286</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.76</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2798</v>
+        <v>-0.2611</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.5546</v>
+        <v>-7.0497</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.63</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3997</v>
+        <v>-0.3884</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.7919</v>
+        <v>-10.4868</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>0.9596</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J302" t="n">
-        <v>24.9496</v>
+        <v>24.5986</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.679</v>
+        <v>0.6674</v>
       </c>
       <c r="J303" t="n">
-        <v>17.654</v>
+        <v>17.3524</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.27</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6201</v>
+        <v>0.6112</v>
       </c>
       <c r="J304" t="n">
-        <v>16.1226</v>
+        <v>15.8912</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.22</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5448</v>
+        <v>0.5396</v>
       </c>
       <c r="J305" t="n">
-        <v>14.1648</v>
+        <v>14.0296</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2147</v>
+        <v>-0.1811</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.5822</v>
+        <v>-4.7086</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.95</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0612</v>
+        <v>-0.049</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.5912</v>
+        <v>-1.274</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.91</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.113</v>
+        <v>-0.0984</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.938</v>
+        <v>-2.5584</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2322</v>
+        <v>-0.2157</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.0372</v>
+        <v>-5.6082</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3789</v>
+        <v>-0.3659</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.8514</v>
+        <v>-9.513400000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4501</v>
+        <v>-0.4432</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.7026</v>
+        <v>-11.5232</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.4</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6665</v>
+        <v>0.6351</v>
       </c>
       <c r="J312" t="n">
-        <v>17.9955</v>
+        <v>17.1477</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3069</v>
+        <v>0.256</v>
       </c>
       <c r="J313" t="n">
-        <v>8.286300000000001</v>
+        <v>6.912</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.01</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0424</v>
+        <v>0.029</v>
       </c>
       <c r="J314" t="n">
-        <v>1.1448</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.84</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2132</v>
+        <v>-0.1925</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.7564</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3581</v>
+        <v>-0.3442</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.668699999999999</v>
+        <v>-9.2934</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.47</v>
       </c>
       <c r="I317" t="n">
-        <v>0.9319</v>
+        <v>0.9179</v>
       </c>
       <c r="J317" t="n">
-        <v>25.1613</v>
+        <v>24.7833</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6829</v>
+        <v>0.668</v>
       </c>
       <c r="J318" t="n">
-        <v>18.4383</v>
+        <v>18.036</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1818</v>
+        <v>0.1541</v>
       </c>
       <c r="J319" t="n">
-        <v>4.9086</v>
+        <v>4.1607</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1818</v>
+        <v>0.1541</v>
       </c>
       <c r="J320" t="n">
-        <v>4.9086</v>
+        <v>4.1607</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6808</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J321" t="n">
-        <v>-18.3816</v>
+        <v>-17.5149</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.43</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5127</v>
+        <v>0.4708</v>
       </c>
       <c r="J322" t="n">
-        <v>11.7921</v>
+        <v>10.8284</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.39</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4825</v>
+        <v>0.4323</v>
       </c>
       <c r="J323" t="n">
-        <v>11.0975</v>
+        <v>9.9429</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.31</v>
       </c>
       <c r="I324" t="n">
-        <v>0.4145</v>
+        <v>0.355</v>
       </c>
       <c r="J324" t="n">
-        <v>9.5335</v>
+        <v>8.164999999999999</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.26</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3607</v>
+        <v>0.305</v>
       </c>
       <c r="J325" t="n">
-        <v>8.296099999999999</v>
+        <v>7.015</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2907</v>
+        <v>0.2414</v>
       </c>
       <c r="J326" t="n">
-        <v>6.6861</v>
+        <v>5.5522</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.98</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.0026</v>
+        <v>0.0111</v>
       </c>
       <c r="J327" t="n">
-        <v>-0.0598</v>
+        <v>0.2553</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1145</v>
+        <v>-0.0989</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.6335</v>
+        <v>-2.2747</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.61</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3989</v>
+        <v>-0.3878</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.1747</v>
+        <v>-8.9194</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.6</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4078</v>
+        <v>-0.3973</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.3794</v>
+        <v>-9.1379</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5048</v>
+        <v>-0.5037</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.6104</v>
+        <v>-11.5851</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.91</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0916</v>
+        <v>-0.0742</v>
       </c>
       <c r="J332" t="n">
-        <v>-2.1068</v>
+        <v>-1.7066</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.71</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.3058</v>
+        <v>-0.2931</v>
       </c>
       <c r="J333" t="n">
-        <v>-7.0334</v>
+        <v>-6.7413</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.315</v>
+        <v>-0.3024</v>
       </c>
       <c r="J334" t="n">
-        <v>-7.245</v>
+        <v>-6.9552</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3846</v>
+        <v>-0.3735</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.845800000000001</v>
+        <v>-8.5905</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5604</v>
+        <v>-0.5665</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.8892</v>
+        <v>-13.0295</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.75</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2478</v>
+        <v>1.2467</v>
       </c>
       <c r="J337" t="n">
-        <v>28.6994</v>
+        <v>28.6741</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.49</v>
       </c>
       <c r="I338" t="n">
-        <v>0.9149</v>
+        <v>0.9029</v>
       </c>
       <c r="J338" t="n">
-        <v>21.0427</v>
+        <v>20.7667</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.46</v>
       </c>
       <c r="I339" t="n">
-        <v>0.875</v>
+        <v>0.8631</v>
       </c>
       <c r="J339" t="n">
-        <v>20.125</v>
+        <v>19.8513</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4672</v>
+        <v>0.4474</v>
       </c>
       <c r="J340" t="n">
-        <v>10.7456</v>
+        <v>10.2902</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.96</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2328</v>
+        <v>-0.2019</v>
       </c>
       <c r="J341" t="n">
-        <v>-5.3544</v>
+        <v>-4.6437</v>
       </c>
     </row>
   </sheetData>
